--- a/datasets/dict/dict.xlsx
+++ b/datasets/dict/dict.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yonghyunnam/Library/Mobile Documents/com~apple~CloudDocs/DeskTop/coding_main/HanTalk/규칙_및_예문_자동화/datasets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yonghyunnam/coding/HanTalk_group/HanTalk/rule_example_auto/datasets/dict/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3604EAE2-4137-6646-A9F9-02ABD88F422C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DF598C0-B77B-474F-A66F-FD612C3A51D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="640" windowWidth="34560" windowHeight="21700" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="640" windowWidth="34560" windowHeight="21700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="items" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="135">
   <si>
     <t>e_id</t>
   </si>
@@ -48,426 +48,432 @@
     <t>ruleset_id</t>
   </si>
   <si>
+    <t>comp_id</t>
+  </si>
+  <si>
+    <t>pattern</t>
+  </si>
+  <si>
+    <t>priority</t>
+  </si>
+  <si>
+    <t>c1</t>
+  </si>
+  <si>
+    <t>detect</t>
+  </si>
+  <si>
+    <t>raw_sentence</t>
+  </si>
+  <si>
+    <t>verify</t>
+  </si>
+  <si>
+    <t>r"(?:는데다가|는\s*데다가|데다가)"</t>
+  </si>
+  <si>
+    <t>(?:가운데|그런데|군데|데다가|[펜엔]데믹)</t>
+  </si>
+  <si>
+    <t>(?:^|[^가-힣])운데(?:$|[^가-힣])</t>
+  </si>
+  <si>
+    <t>canonical_form</t>
+  </si>
+  <si>
+    <t>polyset_id</t>
+  </si>
+  <si>
+    <t>disconti_allowed</t>
+  </si>
+  <si>
+    <t>detect_ruleset_id</t>
+  </si>
+  <si>
+    <t>verify_ruleset_id</t>
+  </si>
+  <si>
+    <t>gloss</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>ps_neunde</t>
+  </si>
+  <si>
+    <t>comp_surf</t>
+  </si>
+  <si>
+    <t>is_required</t>
+  </si>
+  <si>
+    <t>anchor_rank</t>
+  </si>
+  <si>
+    <t>comp_order</t>
+  </si>
+  <si>
+    <t>order_policy</t>
+  </si>
+  <si>
+    <t>fx</t>
+  </si>
+  <si>
+    <t>ㄴ/은/는데</t>
+  </si>
+  <si>
+    <t>hard_fail</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(?:[간갠갼걘건겐견곈곤관괜괸굔군권궨귄균근긘긴깐깬꺈꺤껀껜껸꼔꼰꽌꽨꾄꾠꾼꿘꿴뀐뀬끈끤낀난낸냔냰넌넨년녠논놘놴뇐뇬눈눤뉀뉜뉸는늰닌단댄댠댼던덴뎐뎬돈돤됀된됸둔둰뒌뒨듄든듼딘딴땐땬떈떤뗀뗜뗸똔똰뙌뙨뚄뚠뚼뛘뛴뜐뜬띈띤란랜랸럔런렌련롄론롼뢘뢴룐룬뤈뤤륀륜른린만맨먄먠먼멘면몐몬뫈뫤묀묜문뭔뭰뮌뮨믄믠민반밴뱐뱬번벤변볜본봔봰뵌뵨분붠붼뷘뷴븐븬빈빤뺀뺜뺸뻔뻰뼌뼨뽄뽠뽼뾘뾴뿐뿬쀈쀤쁀쁜쁸삔산샌샨섄선센션셴손솬쇈쇤숀순숸쉔쉰슌슨싄신싼쌘쌴썐썬쎈쎤쏀쏜쏸쐔쐰쑌쑨쒄쒠쒼쓘쓴씐씬안앤얀얜언엔연옌온완왠왼욘운원웬윈윤은읜인잔잰쟌쟨전젠젼졘존좐좬죈죤준줜줸쥔쥰즌즨진짠짼쨘쨴쩐쩬쪈쪤쫀쫜쫸쬔쬰쭌쭨쮄쮠쮼쯘쯴찐찬챈챤첀천첸쳔쳰촌촨쵄쵠쵼춘춴췐췬츈츤칀친칸캔캰컌컨켄켠켼콘콴쾐쾬쿈쿤퀀퀜퀸큔큰킌킨탄탠탼턘턴텐텬톈톤퇀퇜퇸툔툰퉌퉨튄튠튼틘틴판팬퍈퍤펀펜편폔폰퐌퐨푄푠푼풘풴퓐퓬픈픤핀한핸햔햰헌헨현혠혼환홴횐횬훈훤휀휜휸흔흰힌]|[ㄴ]|는)데(?:요)?(?![.?!~…]+)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>앞절의 상황·배경을 제시하고 뒤절로 이어지게 하는 연결어미.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>앞절과 뒤절이 대조·대립 혹은 양보적 전환, 반전되는 관계로 이어질 때 쓰는 연결어미.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>고 말1</t>
+  </si>
+  <si>
+    <t>ps_go_mal</t>
+  </si>
+  <si>
+    <t>c1;c2</t>
+  </si>
+  <si>
+    <t>일어나지 않았으면 좋았을 어떤 일이 끝내 일어났음을 나타내며 동시에 그 일이 일어난 것에 대한 화자의 안타까움을 나타낼 때 쓴다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>고 말2</t>
+  </si>
+  <si>
+    <t>이루기 쉽지 않은 어떤 일을 이루고자 하는 화자의 의지를 나타낼 때 쓴다.</t>
+  </si>
+  <si>
+    <t>고</t>
+  </si>
+  <si>
+    <t>말</t>
+  </si>
+  <si>
+    <t>c2</t>
+  </si>
+  <si>
+    <t>고(?!\s*정말)(?!\s*,)[^\n]{0,2}?(?&lt;!연)(?&lt;!월)(?&lt;!주)(?&lt;!아무)(?&lt;!회)(?&lt;!반)(?&lt;!막)(?&lt;!고추 )말(?!\s*(?:실수|다툼|싸움|보다|했|할|하|씀|해|한|함|을|은|이|에|도|만|들|끝|문|풍선|렸|릴|리|린|려|미|수|로|소|라|고|자|바))(?!(?:실수|다툼|싸움|보다|했|할|하|씀|해|한|함|을|은|이|에|도|만|들|끝|문|풍선|렸|릴|리|린|려|미|수|로|소|라|고|자|바))</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>까지1</t>
+  </si>
+  <si>
+    <t>ps_kkaji</t>
+  </si>
+  <si>
+    <t>까지</t>
+  </si>
+  <si>
+    <t>범위의 끝 지점이나 한계를 나타냄.</t>
+  </si>
+  <si>
+    <t>까지2</t>
+  </si>
+  <si>
+    <t>현재의 상태나 정도에서 더해지거나 더 나아감을 나타냄.</t>
+  </si>
+  <si>
+    <t>까지3</t>
+  </si>
+  <si>
+    <t>정상적인 정도를 지나침을 나타냄.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>까\s*지</t>
+  </si>
+  <si>
+    <t>다면</t>
+  </si>
+  <si>
+    <t>어떤 사실이나 상황을 가정하여 조건으로 삼는 것을 나타냄.</t>
+  </si>
+  <si>
+    <t>ㄴ/은 적 있/없</t>
+  </si>
+  <si>
+    <t>c1;c2;c3</t>
+  </si>
+  <si>
+    <t>어떤 행위나 상태를 해 본 경험이 있거나 없음을 나타냄.</t>
+  </si>
+  <si>
+    <t>ㄴ/은</t>
+  </si>
+  <si>
+    <t>적</t>
+  </si>
+  <si>
+    <t>있/없</t>
+  </si>
+  <si>
+    <t>c3</t>
+  </si>
+  <si>
+    <t>(?:는다면|ㄴ다면|다면)</t>
+  </si>
+  <si>
+    <t>(?:다면서|다\s*면서)</t>
+  </si>
+  <si>
+    <t>적(?:\s*(?:이|가|은|는|도|만|조차|까지))?[^\n]{0,200}?(?:있|없)</t>
+  </si>
+  <si>
+    <t>ㄴ/은/는데1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄴ/은/는데2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ce002</t>
+  </si>
+  <si>
+    <t>ce002</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ce003</t>
+  </si>
+  <si>
+    <t>ce003</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>df004</t>
+  </si>
+  <si>
+    <t>df004</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>df005</t>
+  </si>
+  <si>
+    <t>df005</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>pt001</t>
+  </si>
+  <si>
+    <t>pt001</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>pt002</t>
+  </si>
+  <si>
+    <t>pt002</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>pt003</t>
+  </si>
+  <si>
+    <t>pt003</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ce001</t>
+  </si>
+  <si>
+    <t>ce001</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>df003</t>
+  </si>
+  <si>
+    <t>df003</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>target</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>raw_sentence</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>stage</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>c</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>난이도</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>rs_ce002_d01</t>
+  </si>
+  <si>
+    <t>rs_ce002_v01</t>
+  </si>
+  <si>
+    <t>rs_ce003_d01</t>
+  </si>
+  <si>
+    <t>rs_ce003_v01</t>
+  </si>
+  <si>
+    <t>rs_ce001_d01</t>
+  </si>
+  <si>
+    <t>rs_ce001_v01</t>
+  </si>
+  <si>
+    <t>r_ce002_d01</t>
+  </si>
+  <si>
+    <t>r_ce002_d02</t>
+  </si>
+  <si>
+    <t>r_ce002_v03</t>
+  </si>
+  <si>
+    <t>r_ce002_v06</t>
+  </si>
+  <si>
+    <t>r_ce002_v07</t>
+  </si>
+  <si>
+    <t>r_ce003_d01</t>
+  </si>
+  <si>
+    <t>r_ce003_d02</t>
+  </si>
+  <si>
+    <t>r_ce003_v03</t>
+  </si>
+  <si>
+    <t>r_ce003_v06</t>
+  </si>
+  <si>
+    <t>r_ce003_v07</t>
+  </si>
+  <si>
+    <t>r_ce001_d01</t>
+  </si>
+  <si>
+    <t>r_ce001_v01</t>
+  </si>
+  <si>
+    <t>rs_df004_d01</t>
+  </si>
+  <si>
+    <t>rs_df004_v01</t>
+  </si>
+  <si>
+    <t>rs_df005_d01</t>
+  </si>
+  <si>
+    <t>rs_df005_v01</t>
+  </si>
+  <si>
+    <t>rs_df003_d01</t>
+  </si>
+  <si>
+    <t>rs_df003_v01</t>
+  </si>
+  <si>
+    <t>r_df004_d01</t>
+  </si>
+  <si>
+    <t>r_df005_d01</t>
+  </si>
+  <si>
+    <t>r_df003_d01</t>
+  </si>
+  <si>
+    <t>rs_pt001_d01</t>
+  </si>
+  <si>
+    <t>rs_pt001_v01</t>
+  </si>
+  <si>
+    <t>rs_pt002_d01</t>
+  </si>
+  <si>
+    <t>rs_pt002_v01</t>
+  </si>
+  <si>
+    <t>rs_pt003_d01</t>
+  </si>
+  <si>
+    <t>rs_pt003_v01</t>
+  </si>
+  <si>
+    <t>r_pt001_d01</t>
+  </si>
+  <si>
+    <t>r_pt001_d02</t>
+  </si>
+  <si>
+    <t>r_pt002_d01</t>
+  </si>
+  <si>
+    <t>r_pt002_d02</t>
+  </si>
+  <si>
+    <t>r_pt003_d01</t>
+  </si>
+  <si>
+    <t>r_pt003_d02</t>
+  </si>
+  <si>
+    <t>e_comp_id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>min_gap_to_next</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>max_gap_to_next</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>char_window</t>
+  </si>
+  <si>
     <t>rule_id</t>
-  </si>
-  <si>
-    <t>comp_id</t>
-  </si>
-  <si>
-    <t>pattern</t>
-  </si>
-  <si>
-    <t>priority</t>
-  </si>
-  <si>
-    <t>c1</t>
-  </si>
-  <si>
-    <t>detect</t>
-  </si>
-  <si>
-    <t>raw_sentence</t>
-  </si>
-  <si>
-    <t>verify</t>
-  </si>
-  <si>
-    <t>r"(?:는데다가|는\s*데다가|데다가)"</t>
-  </si>
-  <si>
-    <t>(?:가운데|그런데|군데|데다가|[펜엔]데믹)</t>
-  </si>
-  <si>
-    <t>(?:^|[^가-힣])운데(?:$|[^가-힣])</t>
-  </si>
-  <si>
-    <t>canonical_form</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>group</t>
-  </si>
-  <si>
-    <t>polyset_id</t>
-  </si>
-  <si>
-    <t>disconti_allowed</t>
-  </si>
-  <si>
-    <t>detect_ruleset_id</t>
-  </si>
-  <si>
-    <t>verify_ruleset_id</t>
-  </si>
-  <si>
-    <t>gloss</t>
-  </si>
-  <si>
-    <t>b</t>
-  </si>
-  <si>
-    <t>n</t>
-  </si>
-  <si>
-    <t>y</t>
-  </si>
-  <si>
-    <t>ps_neunde</t>
-  </si>
-  <si>
-    <t>comp_surf</t>
-  </si>
-  <si>
-    <t>is_required</t>
-  </si>
-  <si>
-    <t>anchor_rank</t>
-  </si>
-  <si>
-    <t>comp_order</t>
-  </si>
-  <si>
-    <t>order_policy</t>
-  </si>
-  <si>
-    <t>fx</t>
-  </si>
-  <si>
-    <t>ㄴ/은/는데</t>
-  </si>
-  <si>
-    <t>hard_fail</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>(?:[간갠갼걘건겐견곈곤관괜괸굔군권궨귄균근긘긴깐깬꺈꺤껀껜껸꼔꼰꽌꽨꾄꾠꾼꿘꿴뀐뀬끈끤낀난낸냔냰넌넨년녠논놘놴뇐뇬눈눤뉀뉜뉸는늰닌단댄댠댼던덴뎐뎬돈돤됀된됸둔둰뒌뒨듄든듼딘딴땐땬떈떤뗀뗜뗸똔똰뙌뙨뚄뚠뚼뛘뛴뜐뜬띈띤란랜랸럔런렌련롄론롼뢘뢴룐룬뤈뤤륀륜른린만맨먄먠먼멘면몐몬뫈뫤묀묜문뭔뭰뮌뮨믄믠민반밴뱐뱬번벤변볜본봔봰뵌뵨분붠붼뷘뷴븐븬빈빤뺀뺜뺸뻔뻰뼌뼨뽄뽠뽼뾘뾴뿐뿬쀈쀤쁀쁜쁸삔산샌샨섄선센션셴손솬쇈쇤숀순숸쉔쉰슌슨싄신싼쌘쌴썐썬쎈쎤쏀쏜쏸쐔쐰쑌쑨쒄쒠쒼쓘쓴씐씬안앤얀얜언엔연옌온완왠왼욘운원웬윈윤은읜인잔잰쟌쟨전젠젼졘존좐좬죈죤준줜줸쥔쥰즌즨진짠짼쨘쨴쩐쩬쪈쪤쫀쫜쫸쬔쬰쭌쭨쮄쮠쮼쯘쯴찐찬챈챤첀천첸쳔쳰촌촨쵄쵠쵼춘춴췐췬츈츤칀친칸캔캰컌컨켄켠켼콘콴쾐쾬쿈쿤퀀퀜퀸큔큰킌킨탄탠탼턘턴텐텬톈톤퇀퇜퇸툔툰퉌퉨튄튠튼틘틴판팬퍈퍤펀펜편폔폰퐌퐨푄푠푼풘풴퓐퓬픈픤핀한핸햔햰헌헨현혠혼환홴횐횬훈훤휀휜휸흔흰힌]|[ㄴ]|는)데(?:요)?(?![.?!~…]+)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>앞절의 상황·배경을 제시하고 뒤절로 이어지게 하는 연결어미.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>앞절과 뒤절이 대조·대립 혹은 양보적 전환, 반전되는 관계로 이어질 때 쓰는 연결어미.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>고 말1</t>
-  </si>
-  <si>
-    <t>ps_go_mal</t>
-  </si>
-  <si>
-    <t>c1;c2</t>
-  </si>
-  <si>
-    <t>일어나지 않았으면 좋았을 어떤 일이 끝내 일어났음을 나타내며 동시에 그 일이 일어난 것에 대한 화자의 안타까움을 나타낼 때 쓴다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>고 말2</t>
-  </si>
-  <si>
-    <t>이루기 쉽지 않은 어떤 일을 이루고자 하는 화자의 의지를 나타낼 때 쓴다.</t>
-  </si>
-  <si>
-    <t>고</t>
-  </si>
-  <si>
-    <t>말</t>
-  </si>
-  <si>
-    <t>c2</t>
-  </si>
-  <si>
-    <t>고(?!\s*정말)(?!\s*,)[^\n]{0,2}?(?&lt;!연)(?&lt;!월)(?&lt;!주)(?&lt;!아무)(?&lt;!회)(?&lt;!반)(?&lt;!막)(?&lt;!고추 )말(?!\s*(?:실수|다툼|싸움|보다|했|할|하|씀|해|한|함|을|은|이|에|도|만|들|끝|문|풍선|렸|릴|리|린|려|미|수|로|소|라|고|자|바))(?!(?:실수|다툼|싸움|보다|했|할|하|씀|해|한|함|을|은|이|에|도|만|들|끝|문|풍선|렸|릴|리|린|려|미|수|로|소|라|고|자|바))</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>까지1</t>
-  </si>
-  <si>
-    <t>ps_kkaji</t>
-  </si>
-  <si>
-    <t>까지</t>
-  </si>
-  <si>
-    <t>범위의 끝 지점이나 한계를 나타냄.</t>
-  </si>
-  <si>
-    <t>까지2</t>
-  </si>
-  <si>
-    <t>현재의 상태나 정도에서 더해지거나 더 나아감을 나타냄.</t>
-  </si>
-  <si>
-    <t>까지3</t>
-  </si>
-  <si>
-    <t>정상적인 정도를 지나침을 나타냄.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>까\s*지</t>
-  </si>
-  <si>
-    <t>다면</t>
-  </si>
-  <si>
-    <t>어떤 사실이나 상황을 가정하여 조건으로 삼는 것을 나타냄.</t>
-  </si>
-  <si>
-    <t>ㄴ/은 적 있/없</t>
-  </si>
-  <si>
-    <t>c1;c2;c3</t>
-  </si>
-  <si>
-    <t>어떤 행위나 상태를 해 본 경험이 있거나 없음을 나타냄.</t>
-  </si>
-  <si>
-    <t>ㄴ/은</t>
-  </si>
-  <si>
-    <t>적</t>
-  </si>
-  <si>
-    <t>있/없</t>
-  </si>
-  <si>
-    <t>c3</t>
-  </si>
-  <si>
-    <t>(?:는다면|ㄴ다면|다면)</t>
-  </si>
-  <si>
-    <t>(?:다면서|다\s*면서)</t>
-  </si>
-  <si>
-    <t>적(?:\s*(?:이|가|은|는|도|만|조차|까지))?[^\n]{0,200}?(?:있|없)</t>
-  </si>
-  <si>
-    <t>ㄴ/은/는데1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄴ/은/는데2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ce002</t>
-  </si>
-  <si>
-    <t>ce002</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ce003</t>
-  </si>
-  <si>
-    <t>ce003</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>df004</t>
-  </si>
-  <si>
-    <t>df004</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>df005</t>
-  </si>
-  <si>
-    <t>df005</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>pt001</t>
-  </si>
-  <si>
-    <t>pt001</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>pt002</t>
-  </si>
-  <si>
-    <t>pt002</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>pt003</t>
-  </si>
-  <si>
-    <t>pt003</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ce001</t>
-  </si>
-  <si>
-    <t>ce001</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>df003</t>
-  </si>
-  <si>
-    <t>df003</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>target</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>raw_sentence</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>stage</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>c</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>난이도</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>rs_ce002_d01</t>
-  </si>
-  <si>
-    <t>rs_ce002_v01</t>
-  </si>
-  <si>
-    <t>rs_ce003_d01</t>
-  </si>
-  <si>
-    <t>rs_ce003_v01</t>
-  </si>
-  <si>
-    <t>rs_ce001_d01</t>
-  </si>
-  <si>
-    <t>rs_ce001_v01</t>
-  </si>
-  <si>
-    <t>r_ce002_d01</t>
-  </si>
-  <si>
-    <t>r_ce002_d02</t>
-  </si>
-  <si>
-    <t>r_ce002_v03</t>
-  </si>
-  <si>
-    <t>r_ce002_v06</t>
-  </si>
-  <si>
-    <t>r_ce002_v07</t>
-  </si>
-  <si>
-    <t>r_ce003_d01</t>
-  </si>
-  <si>
-    <t>r_ce003_d02</t>
-  </si>
-  <si>
-    <t>r_ce003_v03</t>
-  </si>
-  <si>
-    <t>r_ce003_v06</t>
-  </si>
-  <si>
-    <t>r_ce003_v07</t>
-  </si>
-  <si>
-    <t>r_ce001_d01</t>
-  </si>
-  <si>
-    <t>r_ce001_v01</t>
-  </si>
-  <si>
-    <t>rs_df004_d01</t>
-  </si>
-  <si>
-    <t>rs_df004_v01</t>
-  </si>
-  <si>
-    <t>rs_df005_d01</t>
-  </si>
-  <si>
-    <t>rs_df005_v01</t>
-  </si>
-  <si>
-    <t>rs_df003_d01</t>
-  </si>
-  <si>
-    <t>rs_df003_v01</t>
-  </si>
-  <si>
-    <t>r_df004_d01</t>
-  </si>
-  <si>
-    <t>r_df005_d01</t>
-  </si>
-  <si>
-    <t>r_df003_d01</t>
-  </si>
-  <si>
-    <t>rs_pt001_d01</t>
-  </si>
-  <si>
-    <t>rs_pt001_v01</t>
-  </si>
-  <si>
-    <t>rs_pt002_d01</t>
-  </si>
-  <si>
-    <t>rs_pt002_v01</t>
-  </si>
-  <si>
-    <t>rs_pt003_d01</t>
-  </si>
-  <si>
-    <t>rs_pt003_v01</t>
-  </si>
-  <si>
-    <t>r_pt001_d01</t>
-  </si>
-  <si>
-    <t>r_pt001_d02</t>
-  </si>
-  <si>
-    <t>r_pt002_d01</t>
-  </si>
-  <si>
-    <t>r_pt002_d02</t>
-  </si>
-  <si>
-    <t>r_pt003_d01</t>
-  </si>
-  <si>
-    <t>r_pt003_d02</t>
-  </si>
-  <si>
-    <t>e_comp_id</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>min_gap_to_next</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>max_gap_to_next</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>char_window</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>주제</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -978,305 +984,308 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="12" customWidth="1"/>
     <col min="2" max="2" width="23.28515625" style="12" customWidth="1"/>
     <col min="3" max="3" width="6.42578125" style="12" customWidth="1"/>
-    <col min="4" max="5" width="17.140625" style="12" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" style="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.28515625" style="12" customWidth="1"/>
-    <col min="8" max="8" width="15" style="12" customWidth="1"/>
-    <col min="9" max="9" width="13.85546875" style="12" customWidth="1"/>
-    <col min="10" max="10" width="97" style="13" customWidth="1"/>
+    <col min="4" max="6" width="17.140625" style="12" customWidth="1"/>
+    <col min="7" max="7" width="15.5703125" style="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" style="12" customWidth="1"/>
+    <col min="9" max="9" width="15" style="12" customWidth="1"/>
+    <col min="10" max="10" width="13.85546875" style="12" customWidth="1"/>
+    <col min="11" max="11" width="97" style="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="4" customFormat="1" ht="19" customHeight="1">
+    <row r="1" spans="1:11" s="4" customFormat="1" ht="19" customHeight="1">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="E1" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="G1" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="H1" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="I1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="J1" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="J2" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="F1" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I1" s="9" t="s">
+      <c r="K2" s="12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="K3" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="K4" s="12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="K5" s="12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="19">
+      <c r="A6" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="K6" s="13" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="19">
+      <c r="A7" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="I7" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="19">
+      <c r="A8" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="J8" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="K8" s="13" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="G9" s="12" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="G2" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="I2" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="J2" s="12" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="H3" s="12" t="s">
+      <c r="H9" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="I9" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="J9" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="J3" s="12" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="I4" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="J4" s="12" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="H5" s="12" t="s">
+      <c r="K9" s="12" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="I10" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="J10" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="J5" s="12" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="19">
-      <c r="A6" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="I6" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="J6" s="13" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="19">
-      <c r="A7" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="H7" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="I7" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="J7" s="13" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="19">
-      <c r="A8" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="H8" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="I8" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="J8" s="13" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="G9" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="H9" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="I9" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="J9" s="12" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="B10" s="12" t="s">
+      <c r="K10" s="12" t="s">
         <v>56</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="I10" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="J10" s="12" t="s">
-        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1305,42 +1314,42 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="H1" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1349,21 +1358,21 @@
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -1372,21 +1381,21 @@
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -1395,7 +1404,7 @@
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -1406,16 +1415,16 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -1424,23 +1433,23 @@
         <v>2</v>
       </c>
       <c r="G5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H5"/>
       <c r="I5"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -1449,7 +1458,7 @@
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -1460,16 +1469,16 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -1478,23 +1487,23 @@
         <v>2</v>
       </c>
       <c r="G7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H7"/>
       <c r="I7"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -1503,21 +1512,21 @@
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -1526,21 +1535,21 @@
         <v>1</v>
       </c>
       <c r="G9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -1549,21 +1558,21 @@
         <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -1572,21 +1581,21 @@
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -1595,7 +1604,7 @@
         <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -1606,16 +1615,16 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B13" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C13" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -1624,7 +1633,7 @@
         <v>2</v>
       </c>
       <c r="G13" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -1635,16 +1644,16 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B14" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C14" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D14" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -1653,7 +1662,7 @@
         <v>3</v>
       </c>
       <c r="G14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1686,42 +1695,42 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>2</v>
+        <v>132</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H1" s="6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G2">
         <v>10</v>
@@ -1733,22 +1742,22 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" t="s">
         <v>7</v>
       </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
       <c r="F3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G3">
         <v>20</v>
@@ -1760,22 +1769,22 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F4" t="s">
         <v>9</v>
-      </c>
-      <c r="E4" t="s">
-        <v>87</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
       </c>
       <c r="G4">
         <v>50</v>
@@ -1787,22 +1796,22 @@
     </row>
     <row r="5" spans="1:9" ht="19" customHeight="1">
       <c r="A5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -1814,22 +1823,22 @@
     </row>
     <row r="6" spans="1:9" ht="19" customHeight="1">
       <c r="A6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E6" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <v>6</v>
@@ -1841,22 +1850,22 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" t="s">
         <v>7</v>
       </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
       <c r="F7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G7">
         <v>10</v>
@@ -1868,22 +1877,22 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" t="s">
         <v>7</v>
       </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
       <c r="F8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G8">
         <v>20</v>
@@ -1895,22 +1904,22 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B9" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C9" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" t="s">
         <v>9</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>10</v>
       </c>
       <c r="G9">
         <v>50</v>
@@ -1921,22 +1930,22 @@
     </row>
     <row r="10" spans="1:9" ht="19" customHeight="1">
       <c r="A10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B10" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C10" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E10" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -1947,22 +1956,22 @@
     </row>
     <row r="11" spans="1:9" ht="19" customHeight="1">
       <c r="A11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B11" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C11" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E11" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G11">
         <v>6</v>
@@ -1973,22 +1982,22 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B12" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" t="s">
         <v>7</v>
       </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
       <c r="F12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G12">
         <v>10</v>
@@ -1999,22 +2008,22 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B13" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C13" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" t="s">
         <v>7</v>
       </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
       <c r="F13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G13">
         <v>10</v>
@@ -2025,22 +2034,22 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B14" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C14" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14" t="s">
         <v>7</v>
       </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
       <c r="F14" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G14">
         <v>10</v>
@@ -2051,22 +2060,22 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B15" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C15" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15" t="s">
         <v>7</v>
       </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
       <c r="F15" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G15">
         <v>20</v>
@@ -2077,22 +2086,22 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B16" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C16" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E16" t="s">
         <v>7</v>
       </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
       <c r="F16" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G16">
         <v>10</v>
@@ -2103,22 +2112,22 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B17" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C17" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E17" t="s">
         <v>7</v>
       </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
       <c r="F17" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G17">
         <v>20</v>
@@ -2129,22 +2138,22 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B18" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C18" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D18" t="s">
+        <v>6</v>
+      </c>
+      <c r="E18" t="s">
         <v>7</v>
       </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
       <c r="F18" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G18" s="14">
         <v>10</v>
@@ -2155,22 +2164,22 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B19" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C19" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D19" t="s">
+        <v>6</v>
+      </c>
+      <c r="E19" t="s">
         <v>7</v>
       </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
       <c r="F19" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G19">
         <v>20</v>
@@ -2181,22 +2190,22 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B20" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C20" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D20" t="s">
+        <v>6</v>
+      </c>
+      <c r="E20" t="s">
         <v>7</v>
       </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
       <c r="F20" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G20">
         <v>10</v>
@@ -2207,22 +2216,22 @@
     </row>
     <row r="21" spans="1:8" ht="19">
       <c r="A21" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B21" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C21" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E21" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G21">
         <v>5</v>
@@ -2233,22 +2242,22 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B22" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C22" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D22" t="s">
+        <v>6</v>
+      </c>
+      <c r="E22" t="s">
         <v>7</v>
       </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
       <c r="F22" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G22">
         <v>10</v>

--- a/datasets/dict/dict.xlsx
+++ b/datasets/dict/dict.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yonghyunnam/coding/HanTalk_group/HanTalk/rule_example_auto/datasets/dict/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DF598C0-B77B-474F-A66F-FD612C3A51D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B177108B-B5F0-7B4D-9238-5CD047BA6DE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="34560" windowHeight="21700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="129">
   <si>
     <t>e_id</t>
   </si>
@@ -69,9 +69,6 @@
     <t>verify</t>
   </si>
   <si>
-    <t>r"(?:는데다가|는\s*데다가|데다가)"</t>
-  </si>
-  <si>
     <t>(?:가운데|그런데|군데|데다가|[펜엔]데믹)</t>
   </si>
   <si>
@@ -389,21 +386,12 @@
     <t>rs_df004_d01</t>
   </si>
   <si>
-    <t>rs_df004_v01</t>
-  </si>
-  <si>
     <t>rs_df005_d01</t>
   </si>
   <si>
-    <t>rs_df005_v01</t>
-  </si>
-  <si>
     <t>rs_df003_d01</t>
   </si>
   <si>
-    <t>rs_df003_v01</t>
-  </si>
-  <si>
     <t>r_df004_d01</t>
   </si>
   <si>
@@ -416,21 +404,12 @@
     <t>rs_pt001_d01</t>
   </si>
   <si>
-    <t>rs_pt001_v01</t>
-  </si>
-  <si>
     <t>rs_pt002_d01</t>
   </si>
   <si>
-    <t>rs_pt002_v01</t>
-  </si>
-  <si>
     <t>rs_pt003_d01</t>
   </si>
   <si>
-    <t>rs_pt003_v01</t>
-  </si>
-  <si>
     <t>r_pt001_d01</t>
   </si>
   <si>
@@ -473,6 +452,10 @@
   </si>
   <si>
     <t>주제</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(?:는데다가|는\s*데다가|데다가)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1003,289 +986,271 @@
         <v>0</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="D1" s="10" t="s">
+      <c r="E1" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="G1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="G1" s="9" t="s">
+      <c r="H1" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="I1" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="I1" s="9" t="s">
+      <c r="J1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="K1" s="11" t="s">
         <v>16</v>
-      </c>
-      <c r="K1" s="11" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H2" s="12" t="s">
         <v>5</v>
       </c>
       <c r="I2" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="J2" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="J2" s="12" t="s">
-        <v>90</v>
-      </c>
       <c r="K2" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H3" s="12" t="s">
         <v>5</v>
       </c>
       <c r="I3" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="J3" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="J3" s="12" t="s">
-        <v>92</v>
-      </c>
       <c r="K3" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B4" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D4" s="12" t="s">
+      <c r="G4" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="G4" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" s="12" t="s">
+      <c r="I4" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="K4" s="12" t="s">
         <v>35</v>
-      </c>
-      <c r="I4" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="J4" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="K4" s="12" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B5" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="K5" s="12" t="s">
         <v>37</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="I5" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="J5" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="K5" s="12" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="19">
       <c r="A6" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B6" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>44</v>
-      </c>
       <c r="G6" s="12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H6" s="12" t="s">
         <v>5</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="J6" s="12" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="K6" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="19">
       <c r="A7" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H7" s="12" t="s">
         <v>5</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="J7" s="12" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="K7" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="19">
       <c r="A8" s="12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H8" s="12" t="s">
         <v>5</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="J8" s="12" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C9" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" s="12" t="s">
         <v>18</v>
-      </c>
-      <c r="G9" s="12" t="s">
-        <v>19</v>
       </c>
       <c r="H9" s="12" t="s">
         <v>5</v>
       </c>
       <c r="I9" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="J9" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="J9" s="12" t="s">
-        <v>94</v>
-      </c>
       <c r="K9" s="12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B10" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H10" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="C10" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="H10" s="12" t="s">
+      <c r="I10" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="K10" s="12" t="s">
         <v>55</v>
-      </c>
-      <c r="I10" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="J10" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="K10" s="12" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1314,42 +1279,42 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="H1" s="1" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
         <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1358,21 +1323,21 @@
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -1381,21 +1346,21 @@
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -1404,7 +1369,7 @@
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -1415,16 +1380,16 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" t="s">
         <v>40</v>
       </c>
-      <c r="C5" t="s">
-        <v>41</v>
-      </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -1433,23 +1398,23 @@
         <v>2</v>
       </c>
       <c r="G5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H5"/>
       <c r="I5"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -1458,7 +1423,7 @@
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -1469,16 +1434,16 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" t="s">
         <v>40</v>
       </c>
-      <c r="C7" t="s">
-        <v>41</v>
-      </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -1487,23 +1452,23 @@
         <v>2</v>
       </c>
       <c r="G7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H7"/>
       <c r="I7"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
       </c>
       <c r="D8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -1512,21 +1477,21 @@
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
       </c>
       <c r="D9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -1535,21 +1500,21 @@
         <v>1</v>
       </c>
       <c r="G9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
         <v>5</v>
       </c>
       <c r="D10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -1558,21 +1523,21 @@
         <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C11" t="s">
         <v>5</v>
       </c>
       <c r="D11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -1581,21 +1546,21 @@
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
       </c>
       <c r="D12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -1604,7 +1569,7 @@
         <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -1615,16 +1580,16 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -1633,7 +1598,7 @@
         <v>2</v>
       </c>
       <c r="G13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -1644,16 +1609,16 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" t="s">
         <v>59</v>
       </c>
-      <c r="C14" t="s">
-        <v>60</v>
-      </c>
       <c r="D14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -1662,7 +1627,7 @@
         <v>3</v>
       </c>
       <c r="G14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1695,13 +1660,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>3</v>
@@ -1710,27 +1675,27 @@
         <v>4</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D2" t="s">
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G2">
         <v>10</v>
@@ -1742,13 +1707,13 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D3" t="s">
         <v>6</v>
@@ -1757,7 +1722,7 @@
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G3">
         <v>20</v>
@@ -1769,22 +1734,22 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D4" t="s">
         <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>128</v>
       </c>
       <c r="G4">
         <v>50</v>
@@ -1796,22 +1761,22 @@
     </row>
     <row r="5" spans="1:9" ht="19" customHeight="1">
       <c r="A5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D5" t="s">
         <v>8</v>
       </c>
       <c r="E5" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -1823,22 +1788,22 @@
     </row>
     <row r="6" spans="1:9" ht="19" customHeight="1">
       <c r="A6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D6" t="s">
         <v>8</v>
       </c>
       <c r="E6" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G6">
         <v>6</v>
@@ -1850,13 +1815,13 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D7" t="s">
         <v>6</v>
@@ -1865,7 +1830,7 @@
         <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G7">
         <v>10</v>
@@ -1877,13 +1842,13 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D8" t="s">
         <v>6</v>
@@ -1892,7 +1857,7 @@
         <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G8">
         <v>20</v>
@@ -1904,13 +1869,13 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D9" t="s">
         <v>8</v>
@@ -1919,7 +1884,7 @@
         <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>9</v>
+        <v>128</v>
       </c>
       <c r="G9">
         <v>50</v>
@@ -1930,22 +1895,22 @@
     </row>
     <row r="10" spans="1:9" ht="19" customHeight="1">
       <c r="A10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D10" t="s">
         <v>8</v>
       </c>
       <c r="E10" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -1956,22 +1921,22 @@
     </row>
     <row r="11" spans="1:9" ht="19" customHeight="1">
       <c r="A11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D11" t="s">
         <v>8</v>
       </c>
       <c r="E11" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G11">
         <v>6</v>
@@ -1982,13 +1947,13 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C12" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D12" t="s">
         <v>6</v>
@@ -1997,7 +1962,7 @@
         <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G12">
         <v>10</v>
@@ -2008,13 +1973,13 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B13" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C13" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D13" t="s">
         <v>6</v>
@@ -2023,7 +1988,7 @@
         <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G13">
         <v>10</v>
@@ -2034,13 +1999,13 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B14" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C14" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D14" t="s">
         <v>6</v>
@@ -2049,7 +2014,7 @@
         <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G14">
         <v>10</v>
@@ -2060,13 +2025,13 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B15" t="s">
+        <v>112</v>
+      </c>
+      <c r="C15" t="s">
         <v>116</v>
-      </c>
-      <c r="C15" t="s">
-        <v>123</v>
       </c>
       <c r="D15" t="s">
         <v>6</v>
@@ -2075,7 +2040,7 @@
         <v>7</v>
       </c>
       <c r="F15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G15">
         <v>20</v>
@@ -2086,13 +2051,13 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B16" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C16" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="D16" t="s">
         <v>6</v>
@@ -2101,7 +2066,7 @@
         <v>7</v>
       </c>
       <c r="F16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G16">
         <v>10</v>
@@ -2112,13 +2077,13 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B17" t="s">
+        <v>113</v>
+      </c>
+      <c r="C17" t="s">
         <v>118</v>
-      </c>
-      <c r="C17" t="s">
-        <v>125</v>
       </c>
       <c r="D17" t="s">
         <v>6</v>
@@ -2127,7 +2092,7 @@
         <v>7</v>
       </c>
       <c r="F17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G17">
         <v>20</v>
@@ -2138,13 +2103,13 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B18" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="C18" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="D18" t="s">
         <v>6</v>
@@ -2153,7 +2118,7 @@
         <v>7</v>
       </c>
       <c r="F18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G18" s="14">
         <v>10</v>
@@ -2164,13 +2129,13 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B19" t="s">
+        <v>114</v>
+      </c>
+      <c r="C19" t="s">
         <v>120</v>
-      </c>
-      <c r="C19" t="s">
-        <v>127</v>
       </c>
       <c r="D19" t="s">
         <v>6</v>
@@ -2179,7 +2144,7 @@
         <v>7</v>
       </c>
       <c r="F19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G19">
         <v>20</v>
@@ -2190,13 +2155,13 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C20" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D20" t="s">
         <v>6</v>
@@ -2205,7 +2170,7 @@
         <v>7</v>
       </c>
       <c r="F20" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G20">
         <v>10</v>
@@ -2216,22 +2181,22 @@
     </row>
     <row r="21" spans="1:8" ht="19">
       <c r="A21" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C21" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D21" t="s">
         <v>8</v>
       </c>
       <c r="E21" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G21">
         <v>5</v>
@@ -2242,13 +2207,13 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B22" t="s">
+        <v>108</v>
+      </c>
+      <c r="C22" t="s">
         <v>111</v>
-      </c>
-      <c r="C22" t="s">
-        <v>115</v>
       </c>
       <c r="D22" t="s">
         <v>6</v>
@@ -2257,7 +2222,7 @@
         <v>7</v>
       </c>
       <c r="F22" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G22">
         <v>10</v>

--- a/datasets/dict/dict.xlsx
+++ b/datasets/dict/dict.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yonghyunnam/coding/HanTalk_group/HanTalk/rule_example_auto/datasets/dict/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B177108B-B5F0-7B4D-9238-5CD047BA6DE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEAEEDA9-A34E-C046-B15C-9299EADC1DE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="640" windowWidth="34560" windowHeight="21700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="640" windowWidth="34560" windowHeight="21700" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="items" sheetId="1" r:id="rId1"/>
@@ -22,440 +22,391 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">items!$A$1:$A$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">rule_components!$A$1:$A$3</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="124">
   <si>
     <t>e_id</t>
   </si>
   <si>
+    <t>canonical_form</t>
+  </si>
+  <si>
+    <t>group</t>
+  </si>
+  <si>
+    <t>polyset_id</t>
+  </si>
+  <si>
+    <t>난이도</t>
+  </si>
+  <si>
+    <t>주제</t>
+  </si>
+  <si>
+    <t>disconti_allowed</t>
+  </si>
+  <si>
+    <t>e_comp_id</t>
+  </si>
+  <si>
+    <t>detect_ruleset_id</t>
+  </si>
+  <si>
+    <t>verify_ruleset_id</t>
+  </si>
+  <si>
+    <t>gloss</t>
+  </si>
+  <si>
+    <t>ce002</t>
+  </si>
+  <si>
+    <t>ㄴ/은/는데1</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>ps_neunde</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>c1</t>
+  </si>
+  <si>
+    <t>rs_ce002_d01</t>
+  </si>
+  <si>
+    <t>rs_ce002_v01</t>
+  </si>
+  <si>
+    <t>앞절의 상황·배경을 제시하고 뒤절로 이어지게 하는 연결어미.</t>
+  </si>
+  <si>
+    <t>ce003</t>
+  </si>
+  <si>
+    <t>ㄴ/은/는데2</t>
+  </si>
+  <si>
+    <t>rs_ce003_d01</t>
+  </si>
+  <si>
+    <t>rs_ce003_v01</t>
+  </si>
+  <si>
+    <t>앞절과 뒤절이 대조·대립 혹은 양보적 전환, 반전되는 관계로 이어질 때 쓰는 연결어미.</t>
+  </si>
+  <si>
+    <t>df004</t>
+  </si>
+  <si>
+    <t>고 말1</t>
+  </si>
+  <si>
+    <t>ps_go_mal</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>c1;c2</t>
+  </si>
+  <si>
+    <t>rs_df004_d01</t>
+  </si>
+  <si>
+    <t>일어나지 않았으면 좋았을 어떤 일이 끝내 일어났음을 나타내며 동시에 그 일이 일어난 것에 대한 화자의 안타까움을 나타낼 때 쓴다.</t>
+  </si>
+  <si>
+    <t>df005</t>
+  </si>
+  <si>
+    <t>고 말2</t>
+  </si>
+  <si>
+    <t>rs_df005_d01</t>
+  </si>
+  <si>
+    <t>이루기 쉽지 않은 어떤 일을 이루고자 하는 화자의 의지를 나타낼 때 쓴다.</t>
+  </si>
+  <si>
+    <t>pt001</t>
+  </si>
+  <si>
+    <t>까지1</t>
+  </si>
+  <si>
+    <t>ps_kkaji</t>
+  </si>
+  <si>
+    <t>rs_pt001_d01</t>
+  </si>
+  <si>
+    <t>범위의 끝 지점이나 한계를 나타냄.</t>
+  </si>
+  <si>
+    <t>pt002</t>
+  </si>
+  <si>
+    <t>까지2</t>
+  </si>
+  <si>
+    <t>rs_pt002_d01</t>
+  </si>
+  <si>
+    <t>현재의 상태나 정도에서 더해지거나 더 나아감을 나타냄.</t>
+  </si>
+  <si>
+    <t>pt003</t>
+  </si>
+  <si>
+    <t>까지3</t>
+  </si>
+  <si>
+    <t>rs_pt003_d01</t>
+  </si>
+  <si>
+    <t>정상적인 정도를 지나침을 나타냄.</t>
+  </si>
+  <si>
+    <t>ce001</t>
+  </si>
+  <si>
+    <t>다면</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>rs_ce001_d01</t>
+  </si>
+  <si>
+    <t>rs_ce001_v01</t>
+  </si>
+  <si>
+    <t>어떤 사실이나 상황을 가정하여 조건으로 삼는 것을 나타냄.</t>
+  </si>
+  <si>
+    <t>df003</t>
+  </si>
+  <si>
+    <t>ㄴ/은 적 있/없</t>
+  </si>
+  <si>
+    <t>c1;c2;c3</t>
+  </si>
+  <si>
+    <t>rs_df003_d01</t>
+  </si>
+  <si>
+    <t>어떤 행위나 상태를 해 본 경험이 있거나 없음을 나타냄.</t>
+  </si>
+  <si>
+    <t>comp_surf</t>
+  </si>
+  <si>
+    <t>is_required</t>
+  </si>
+  <si>
+    <t>anchor_rank</t>
+  </si>
+  <si>
+    <t>min_gap_to_next</t>
+  </si>
+  <si>
+    <t>max_gap_to_next</t>
+  </si>
+  <si>
+    <t>ㄴ/은/는데</t>
+  </si>
+  <si>
+    <t>fx</t>
+  </si>
+  <si>
+    <t>고</t>
+  </si>
+  <si>
+    <t>말</t>
+  </si>
+  <si>
+    <t>c2</t>
+  </si>
+  <si>
+    <t>까지</t>
+  </si>
+  <si>
+    <t>적</t>
+  </si>
+  <si>
+    <t>있/없</t>
+  </si>
+  <si>
+    <t>c3</t>
+  </si>
+  <si>
     <t>ruleset_id</t>
   </si>
   <si>
+    <t>rule_id</t>
+  </si>
+  <si>
+    <t>stage</t>
+  </si>
+  <si>
+    <t>target</t>
+  </si>
+  <si>
+    <t>pattern</t>
+  </si>
+  <si>
+    <t>priority</t>
+  </si>
+  <si>
+    <t>hard_fail</t>
+  </si>
+  <si>
+    <t>r_ce002_d01</t>
+  </si>
+  <si>
+    <t>detect</t>
+  </si>
+  <si>
+    <t>raw_sentence</t>
+  </si>
+  <si>
+    <t>(?:[간갠갼걘건겐견곈곤관괜괸굔군권궨귄균근긘긴깐깬꺈꺤껀껜껸꼔꼰꽌꽨꾄꾠꾼꿘꿴뀐뀬끈끤낀난낸냔냰넌넨년녠논놘놴뇐뇬눈눤뉀뉜뉸는늰닌단댄댠댼던덴뎐뎬돈돤됀된됸둔둰뒌뒨듄든듼딘딴땐땬떈떤뗀뗜뗸똔똰뙌뙨뚄뚠뚼뛘뛴뜐뜬띈띤란랜랸럔런렌련롄론롼뢘뢴룐룬뤈뤤륀륜른린만맨먄먠먼멘면몐몬뫈뫤묀묜문뭔뭰뮌뮨믄믠민반밴뱐뱬번벤변볜본봔봰뵌뵨분붠붼뷘뷴븐븬빈빤뺀뺜뺸뻔뻰뼌뼨뽄뽠뽼뾘뾴뿐뿬쀈쀤쁀쁜쁸삔산샌샨섄선센션셴손솬쇈쇤숀순숸쉔쉰슌슨싄신싼쌘쌴썐썬쎈쎤쏀쏜쏸쐔쐰쑌쑨쒄쒠쒼쓘쓴씐씬안앤얀얜언엔연옌온완왠왼욘운원웬윈윤은읜인잔잰쟌쟨전젠젼졘존좐좬죈죤준줜줸쥔쥰즌즨진짠짼쨘쨴쩐쩬쪈쪤쫀쫜쫸쬔쬰쭌쭨쮄쮠쮼쯘쯴찐찬챈챤첀천첸쳔쳰촌촨쵄쵠쵼춘춴췐췬츈츤칀친칸캔캰컌컨켄켠켼콘콴쾐쾬쿈쿤퀀퀜퀸큔큰킌킨탄탠탼턘턴텐텬톈톤퇀퇜퇸툔툰퉌퉨튄튠튼틘틴판팬퍈퍤펀펜편폔폰퐌퐨푄푠푼풘풴퓐퓬픈픤핀한핸햔햰헌헨현혠혼환홴횐횬훈훤휀휜휸흔흰힌]|[ㄴ]|는)데(?:요)?(?![.?!~…]+)</t>
+  </si>
+  <si>
+    <t>r_ce002_d02</t>
+  </si>
+  <si>
+    <t>r_ce002_v03</t>
+  </si>
+  <si>
+    <t>verify</t>
+  </si>
+  <si>
+    <t>(?:는데다가|는\s*데다가|데다가)</t>
+  </si>
+  <si>
+    <t>r_ce002_v06</t>
+  </si>
+  <si>
+    <t>char_window</t>
+  </si>
+  <si>
+    <t>(?:가운데|그런데|군데|데다가|[펜엔]데믹)</t>
+  </si>
+  <si>
+    <t>r_ce002_v07</t>
+  </si>
+  <si>
+    <t>(?:^|[^가-힣])운데(?:$|[^가-힣])</t>
+  </si>
+  <si>
+    <t>r_ce003_d01</t>
+  </si>
+  <si>
+    <t>r_ce003_d02</t>
+  </si>
+  <si>
+    <t>r_ce003_v03</t>
+  </si>
+  <si>
+    <t>r_ce003_v06</t>
+  </si>
+  <si>
+    <t>r_ce003_v07</t>
+  </si>
+  <si>
+    <t>r_df004_d01</t>
+  </si>
+  <si>
+    <t>고(?!\s*정말)(?!\s*,)[^\n]{0,2}?(?&lt;!연)(?&lt;!월)(?&lt;!주)(?&lt;!아무)(?&lt;!회)(?&lt;!반)(?&lt;!막)(?&lt;!고추 )말(?!\s*(?:실수|다툼|싸움|보다|했|할|하|씀|해|한|함|을|은|이|에|도|만|들|끝|문|풍선|렸|릴|리|린|려|미|수|로|소|라|고|자|바))(?!(?:실수|다툼|싸움|보다|했|할|하|씀|해|한|함|을|은|이|에|도|만|들|끝|문|풍선|렸|릴|리|린|려|미|수|로|소|라|고|자|바))</t>
+  </si>
+  <si>
+    <t>r_df005_d01</t>
+  </si>
+  <si>
+    <t>r_pt001_d01</t>
+  </si>
+  <si>
+    <t>r_pt001_d02</t>
+  </si>
+  <si>
+    <t>까\s*지</t>
+  </si>
+  <si>
+    <t>r_pt002_d01</t>
+  </si>
+  <si>
+    <t>r_pt002_d02</t>
+  </si>
+  <si>
+    <t>r_pt003_d01</t>
+  </si>
+  <si>
+    <t>r_pt003_d02</t>
+  </si>
+  <si>
+    <t>r_ce001_d01</t>
+  </si>
+  <si>
+    <t>(?:는다면|ㄴ다면|다면)</t>
+  </si>
+  <si>
+    <t>r_ce001_v01</t>
+  </si>
+  <si>
+    <t>(?:다면서|다\s*면서)</t>
+  </si>
+  <si>
+    <t>r_df003_d01</t>
+  </si>
+  <si>
+    <t>적(?:\s*(?:이|가|은|는|도|만|조차|까지))?[^\n]{0,200}?(?:있|없)</t>
+  </si>
+  <si>
+    <t>comp_order</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>order_policy</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>comp_id</t>
-  </si>
-  <si>
-    <t>pattern</t>
-  </si>
-  <si>
-    <t>priority</t>
-  </si>
-  <si>
-    <t>c1</t>
-  </si>
-  <si>
-    <t>detect</t>
-  </si>
-  <si>
-    <t>raw_sentence</t>
-  </si>
-  <si>
-    <t>verify</t>
-  </si>
-  <si>
-    <t>(?:가운데|그런데|군데|데다가|[펜엔]데믹)</t>
-  </si>
-  <si>
-    <t>(?:^|[^가-힣])운데(?:$|[^가-힣])</t>
-  </si>
-  <si>
-    <t>canonical_form</t>
-  </si>
-  <si>
-    <t>polyset_id</t>
-  </si>
-  <si>
-    <t>disconti_allowed</t>
-  </si>
-  <si>
-    <t>detect_ruleset_id</t>
-  </si>
-  <si>
-    <t>verify_ruleset_id</t>
-  </si>
-  <si>
-    <t>gloss</t>
-  </si>
-  <si>
-    <t>b</t>
-  </si>
-  <si>
-    <t>n</t>
-  </si>
-  <si>
-    <t>y</t>
-  </si>
-  <si>
-    <t>ps_neunde</t>
-  </si>
-  <si>
-    <t>comp_surf</t>
-  </si>
-  <si>
-    <t>is_required</t>
-  </si>
-  <si>
-    <t>anchor_rank</t>
-  </si>
-  <si>
-    <t>comp_order</t>
-  </si>
-  <si>
-    <t>order_policy</t>
-  </si>
-  <si>
-    <t>fx</t>
-  </si>
-  <si>
-    <t>ㄴ/은/는데</t>
-  </si>
-  <si>
-    <t>hard_fail</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>(?:[간갠갼걘건겐견곈곤관괜괸굔군권궨귄균근긘긴깐깬꺈꺤껀껜껸꼔꼰꽌꽨꾄꾠꾼꿘꿴뀐뀬끈끤낀난낸냔냰넌넨년녠논놘놴뇐뇬눈눤뉀뉜뉸는늰닌단댄댠댼던덴뎐뎬돈돤됀된됸둔둰뒌뒨듄든듼딘딴땐땬떈떤뗀뗜뗸똔똰뙌뙨뚄뚠뚼뛘뛴뜐뜬띈띤란랜랸럔런렌련롄론롼뢘뢴룐룬뤈뤤륀륜른린만맨먄먠먼멘면몐몬뫈뫤묀묜문뭔뭰뮌뮨믄믠민반밴뱐뱬번벤변볜본봔봰뵌뵨분붠붼뷘뷴븐븬빈빤뺀뺜뺸뻔뻰뼌뼨뽄뽠뽼뾘뾴뿐뿬쀈쀤쁀쁜쁸삔산샌샨섄선센션셴손솬쇈쇤숀순숸쉔쉰슌슨싄신싼쌘쌴썐썬쎈쎤쏀쏜쏸쐔쐰쑌쑨쒄쒠쒼쓘쓴씐씬안앤얀얜언엔연옌온완왠왼욘운원웬윈윤은읜인잔잰쟌쟨전젠젼졘존좐좬죈죤준줜줸쥔쥰즌즨진짠짼쨘쨴쩐쩬쪈쪤쫀쫜쫸쬔쬰쭌쭨쮄쮠쮼쯘쯴찐찬챈챤첀천첸쳔쳰촌촨쵄쵠쵼춘춴췐췬츈츤칀친칸캔캰컌컨켄켠켼콘콴쾐쾬쿈쿤퀀퀜퀸큔큰킌킨탄탠탼턘턴텐텬톈톤퇀퇜퇸툔툰퉌퉨튄튠튼틘틴판팬퍈퍤펀펜편폔폰퐌퐨푄푠푼풘풴퓐퓬픈픤핀한핸햔햰헌헨현혠혼환홴횐횬훈훤휀휜휸흔흰힌]|[ㄴ]|는)데(?:요)?(?![.?!~…]+)</t>
+    <t>bridge_id</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>앞절의 상황·배경을 제시하고 뒤절로 이어지게 하는 연결어미.</t>
+    <t>adnominal_n</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>앞절과 뒤절이 대조·대립 혹은 양보적 전환, 반전되는 관계로 이어질 때 쓰는 연결어미.</t>
+    <t>ㄴ/은</t>
     <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>고 말1</t>
-  </si>
-  <si>
-    <t>ps_go_mal</t>
-  </si>
-  <si>
-    <t>c1;c2</t>
-  </si>
-  <si>
-    <t>일어나지 않았으면 좋았을 어떤 일이 끝내 일어났음을 나타내며 동시에 그 일이 일어난 것에 대한 화자의 안타까움을 나타낼 때 쓴다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>고 말2</t>
-  </si>
-  <si>
-    <t>이루기 쉽지 않은 어떤 일을 이루고자 하는 화자의 의지를 나타낼 때 쓴다.</t>
-  </si>
-  <si>
-    <t>고</t>
-  </si>
-  <si>
-    <t>말</t>
-  </si>
-  <si>
-    <t>c2</t>
-  </si>
-  <si>
-    <t>고(?!\s*정말)(?!\s*,)[^\n]{0,2}?(?&lt;!연)(?&lt;!월)(?&lt;!주)(?&lt;!아무)(?&lt;!회)(?&lt;!반)(?&lt;!막)(?&lt;!고추 )말(?!\s*(?:실수|다툼|싸움|보다|했|할|하|씀|해|한|함|을|은|이|에|도|만|들|끝|문|풍선|렸|릴|리|린|려|미|수|로|소|라|고|자|바))(?!(?:실수|다툼|싸움|보다|했|할|하|씀|해|한|함|을|은|이|에|도|만|들|끝|문|풍선|렸|릴|리|린|려|미|수|로|소|라|고|자|바))</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>까지1</t>
-  </si>
-  <si>
-    <t>ps_kkaji</t>
-  </si>
-  <si>
-    <t>까지</t>
-  </si>
-  <si>
-    <t>범위의 끝 지점이나 한계를 나타냄.</t>
-  </si>
-  <si>
-    <t>까지2</t>
-  </si>
-  <si>
-    <t>현재의 상태나 정도에서 더해지거나 더 나아감을 나타냄.</t>
-  </si>
-  <si>
-    <t>까지3</t>
-  </si>
-  <si>
-    <t>정상적인 정도를 지나침을 나타냄.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>까\s*지</t>
-  </si>
-  <si>
-    <t>다면</t>
-  </si>
-  <si>
-    <t>어떤 사실이나 상황을 가정하여 조건으로 삼는 것을 나타냄.</t>
-  </si>
-  <si>
-    <t>ㄴ/은 적 있/없</t>
-  </si>
-  <si>
-    <t>c1;c2;c3</t>
-  </si>
-  <si>
-    <t>어떤 행위나 상태를 해 본 경험이 있거나 없음을 나타냄.</t>
-  </si>
-  <si>
-    <t>ㄴ/은</t>
-  </si>
-  <si>
-    <t>적</t>
-  </si>
-  <si>
-    <t>있/없</t>
-  </si>
-  <si>
-    <t>c3</t>
-  </si>
-  <si>
-    <t>(?:는다면|ㄴ다면|다면)</t>
-  </si>
-  <si>
-    <t>(?:다면서|다\s*면서)</t>
-  </si>
-  <si>
-    <t>적(?:\s*(?:이|가|은|는|도|만|조차|까지))?[^\n]{0,200}?(?:있|없)</t>
-  </si>
-  <si>
-    <t>ㄴ/은/는데1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄴ/은/는데2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ce002</t>
-  </si>
-  <si>
-    <t>ce002</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ce003</t>
-  </si>
-  <si>
-    <t>ce003</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>df004</t>
-  </si>
-  <si>
-    <t>df004</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>df005</t>
-  </si>
-  <si>
-    <t>df005</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>pt001</t>
-  </si>
-  <si>
-    <t>pt001</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>pt002</t>
-  </si>
-  <si>
-    <t>pt002</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>pt003</t>
-  </si>
-  <si>
-    <t>pt003</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ce001</t>
-  </si>
-  <si>
-    <t>ce001</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>df003</t>
   </si>
   <si>
     <t>df003</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>target</t>
+    <t>ㄴ/은/는데</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>raw_sentence</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>stage</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>c</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>난이도</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>rs_ce002_d01</t>
-  </si>
-  <si>
-    <t>rs_ce002_v01</t>
-  </si>
-  <si>
-    <t>rs_ce003_d01</t>
-  </si>
-  <si>
-    <t>rs_ce003_v01</t>
-  </si>
-  <si>
-    <t>rs_ce001_d01</t>
-  </si>
-  <si>
-    <t>rs_ce001_v01</t>
-  </si>
-  <si>
-    <t>r_ce002_d01</t>
-  </si>
-  <si>
-    <t>r_ce002_d02</t>
-  </si>
-  <si>
-    <t>r_ce002_v03</t>
-  </si>
-  <si>
-    <t>r_ce002_v06</t>
-  </si>
-  <si>
-    <t>r_ce002_v07</t>
-  </si>
-  <si>
-    <t>r_ce003_d01</t>
-  </si>
-  <si>
-    <t>r_ce003_d02</t>
-  </si>
-  <si>
-    <t>r_ce003_v03</t>
-  </si>
-  <si>
-    <t>r_ce003_v06</t>
-  </si>
-  <si>
-    <t>r_ce003_v07</t>
-  </si>
-  <si>
-    <t>r_ce001_d01</t>
-  </si>
-  <si>
-    <t>r_ce001_v01</t>
-  </si>
-  <si>
-    <t>rs_df004_d01</t>
-  </si>
-  <si>
-    <t>rs_df005_d01</t>
-  </si>
-  <si>
-    <t>rs_df003_d01</t>
-  </si>
-  <si>
-    <t>r_df004_d01</t>
-  </si>
-  <si>
-    <t>r_df005_d01</t>
-  </si>
-  <si>
-    <t>r_df003_d01</t>
-  </si>
-  <si>
-    <t>rs_pt001_d01</t>
-  </si>
-  <si>
-    <t>rs_pt002_d01</t>
-  </si>
-  <si>
-    <t>rs_pt003_d01</t>
-  </si>
-  <si>
-    <t>r_pt001_d01</t>
-  </si>
-  <si>
-    <t>r_pt001_d02</t>
-  </si>
-  <si>
-    <t>r_pt002_d01</t>
-  </si>
-  <si>
-    <t>r_pt002_d02</t>
-  </si>
-  <si>
-    <t>r_pt003_d01</t>
-  </si>
-  <si>
-    <t>r_pt003_d02</t>
-  </si>
-  <si>
-    <t>e_comp_id</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>min_gap_to_next</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>max_gap_to_next</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>char_window</t>
-  </si>
-  <si>
-    <t>rule_id</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>group</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>주제</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>(?:는데다가|는\s*데다가|데다가)</t>
+    <t>c1</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -986,271 +937,271 @@
         <v>0</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>126</v>
+        <v>2</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>87</v>
+        <v>4</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>127</v>
+        <v>5</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>121</v>
+        <v>7</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K1" s="11" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="12" t="s">
-        <v>66</v>
+        <v>11</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>63</v>
+        <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>86</v>
+        <v>13</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G2" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="I2" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="J2" s="12" t="s">
-        <v>89</v>
-      </c>
       <c r="K2" s="12" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="12" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>86</v>
+        <v>13</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>91</v>
+        <v>23</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="12" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>86</v>
+        <v>13</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>106</v>
+        <v>30</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="12" t="s">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="B5" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="K5" s="12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="19" customHeight="1">
+      <c r="A6" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="G5" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="I5" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="K5" s="12" t="s">
+      <c r="B6" s="12" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" ht="19">
-      <c r="A6" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="B6" s="12" t="s">
+      <c r="C6" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="K6" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="19" customHeight="1">
+      <c r="A7" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="D6" s="12" t="s">
+      <c r="C7" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="G6" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="I6" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="K6" s="13" t="s">
+      <c r="K7" s="13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="19" customHeight="1">
+      <c r="A8" s="12" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" ht="19">
-      <c r="A7" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="B7" s="12" t="s">
+      <c r="B8" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="H7" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="I7" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="K7" s="13" t="s">
+      <c r="C8" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="12" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" ht="19">
-      <c r="A8" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="B8" s="12" t="s">
+      <c r="K8" s="13" t="s">
         <v>48</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="H8" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="I8" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="K8" s="13" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="12" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="B9" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="12" t="s">
-        <v>17</v>
-      </c>
       <c r="G9" s="12" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>92</v>
+        <v>52</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>93</v>
+        <v>53</v>
       </c>
       <c r="K9" s="12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="12" t="s">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>108</v>
+        <v>58</v>
       </c>
       <c r="K10" s="12" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1263,371 +1214,390 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="17.5703125" style="8" customWidth="1"/>
     <col min="3" max="3" width="12.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="13.42578125" style="8" customWidth="1"/>
-    <col min="7" max="7" width="22.28515625" style="8" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" style="8" customWidth="1"/>
+    <col min="5" max="7" width="13.42578125" style="8" customWidth="1"/>
+    <col min="8" max="8" width="22.28515625" style="8" customWidth="1"/>
+    <col min="9" max="9" width="15.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.140625" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1">
+    <row r="1" spans="1:10" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D2"/>
+      <c r="E2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3"/>
+      <c r="E3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4"/>
+      <c r="E4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4" t="s">
+        <v>66</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" t="s">
         <v>25</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" t="s">
+      <c r="B5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D5"/>
+      <c r="E5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5" t="s">
         <v>66</v>
       </c>
-      <c r="B2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" t="s">
+      <c r="I5"/>
+      <c r="J5"/>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6"/>
+      <c r="E6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6" t="s">
+        <v>66</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" t="s">
         <v>68</v>
       </c>
-      <c r="B3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" t="s">
+      <c r="C7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D7"/>
+      <c r="E7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7" t="s">
+        <v>66</v>
+      </c>
+      <c r="I7"/>
+      <c r="J7"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" t="s">
         <v>70</v>
       </c>
-      <c r="B4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4">
+      <c r="C8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8"/>
+      <c r="E8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9"/>
+      <c r="E9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10"/>
+      <c r="E10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11"/>
+      <c r="E11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B12" t="s">
+        <v>120</v>
+      </c>
+      <c r="C12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" t="s">
+        <v>119</v>
+      </c>
+      <c r="E12" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12">
         <v>0</v>
       </c>
-      <c r="I4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" t="s">
-        <v>70</v>
-      </c>
-      <c r="B5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5"/>
-      <c r="I5"/>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" t="s">
-        <v>72</v>
-      </c>
-      <c r="B6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H6">
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12" t="s">
+        <v>66</v>
+      </c>
+      <c r="I12">
         <v>0</v>
       </c>
-      <c r="I6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" t="s">
-        <v>72</v>
-      </c>
-      <c r="B7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>2</v>
-      </c>
-      <c r="G7" t="s">
-        <v>26</v>
-      </c>
-      <c r="H7"/>
-      <c r="I7"/>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" t="s">
-        <v>74</v>
-      </c>
-      <c r="B8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" t="s">
-        <v>76</v>
-      </c>
-      <c r="B9" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" t="s">
-        <v>78</v>
-      </c>
-      <c r="B10" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" t="s">
-        <v>80</v>
-      </c>
-      <c r="B11" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" t="s">
-        <v>82</v>
-      </c>
-      <c r="B12" t="s">
-        <v>56</v>
-      </c>
-      <c r="C12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D12" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="G12" t="s">
-        <v>26</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
+      <c r="J12">
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="C13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D13" t="s">
-        <v>19</v>
-      </c>
-      <c r="E13">
-        <v>2</v>
+        <v>69</v>
+      </c>
+      <c r="D13"/>
+      <c r="E13" t="s">
+        <v>28</v>
       </c>
       <c r="F13">
         <v>2</v>
       </c>
-      <c r="G13" t="s">
-        <v>26</v>
-      </c>
-      <c r="H13">
+      <c r="G13">
+        <v>2</v>
+      </c>
+      <c r="H13" t="s">
+        <v>66</v>
+      </c>
+      <c r="I13">
         <v>0</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="B14" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="C14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E14">
-        <v>1</v>
+        <v>73</v>
+      </c>
+      <c r="D14"/>
+      <c r="E14" t="s">
+        <v>28</v>
       </c>
       <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
         <v>3</v>
       </c>
-      <c r="G14" t="s">
-        <v>26</v>
+      <c r="H14" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1657,45 +1627,45 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1</v>
+        <v>74</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>3</v>
+        <v>78</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>4</v>
+        <v>79</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>28</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="E2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F2" t="s">
         <v>84</v>
-      </c>
-      <c r="F2" t="s">
-        <v>29</v>
       </c>
       <c r="G2">
         <v>10</v>
@@ -1707,22 +1677,22 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
       <c r="F3" t="s">
-        <v>29</v>
+        <v>84</v>
       </c>
       <c r="G3">
         <v>20</v>
@@ -1734,22 +1704,22 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>8</v>
+        <v>87</v>
       </c>
       <c r="E4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F4" t="s">
-        <v>128</v>
+        <v>88</v>
       </c>
       <c r="G4">
         <v>50</v>
@@ -1761,22 +1731,22 @@
     </row>
     <row r="5" spans="1:9" ht="19" customHeight="1">
       <c r="A5" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
         <v>89</v>
       </c>
-      <c r="C5" t="s">
-        <v>97</v>
-      </c>
       <c r="D5" t="s">
-        <v>8</v>
+        <v>87</v>
       </c>
       <c r="E5" t="s">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>9</v>
+        <v>91</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -1788,22 +1758,22 @@
     </row>
     <row r="6" spans="1:9" ht="19" customHeight="1">
       <c r="A6" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>8</v>
+        <v>87</v>
       </c>
       <c r="E6" t="s">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>10</v>
+        <v>93</v>
       </c>
       <c r="G6">
         <v>6</v>
@@ -1815,22 +1785,22 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
       <c r="F7" t="s">
-        <v>29</v>
+        <v>84</v>
       </c>
       <c r="G7">
         <v>10</v>
@@ -1842,22 +1812,22 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D8" t="s">
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
       <c r="F8" t="s">
-        <v>29</v>
+        <v>84</v>
       </c>
       <c r="G8">
         <v>20</v>
@@ -1869,22 +1839,22 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>91</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D9" t="s">
-        <v>8</v>
+        <v>87</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
       <c r="F9" t="s">
-        <v>128</v>
+        <v>88</v>
       </c>
       <c r="G9">
         <v>50</v>
@@ -1895,22 +1865,22 @@
     </row>
     <row r="10" spans="1:9" ht="19" customHeight="1">
       <c r="A10" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" t="s">
+        <v>97</v>
+      </c>
+      <c r="D10" t="s">
+        <v>87</v>
+      </c>
+      <c r="E10" t="s">
+        <v>90</v>
+      </c>
+      <c r="F10" s="5" t="s">
         <v>91</v>
-      </c>
-      <c r="C10" t="s">
-        <v>102</v>
-      </c>
-      <c r="D10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" t="s">
-        <v>124</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>9</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -1921,22 +1891,22 @@
     </row>
     <row r="11" spans="1:9" ht="19" customHeight="1">
       <c r="A11" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>91</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D11" t="s">
-        <v>8</v>
+        <v>87</v>
       </c>
       <c r="E11" t="s">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>10</v>
+        <v>93</v>
       </c>
       <c r="G11">
         <v>6</v>
@@ -1947,22 +1917,22 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>106</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="D12" t="s">
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
       <c r="F12" t="s">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="G12">
         <v>10</v>
@@ -1973,22 +1943,22 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="B13" t="s">
-        <v>107</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D13" t="s">
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
       <c r="F13" t="s">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="G13">
         <v>10</v>
@@ -1999,22 +1969,22 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>112</v>
+        <v>39</v>
       </c>
       <c r="C14" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="D14" t="s">
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="E14" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
       <c r="F14" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="G14">
         <v>10</v>
@@ -2025,22 +1995,22 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>112</v>
+        <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="D15" t="s">
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="E15" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
       <c r="F15" t="s">
-        <v>50</v>
+        <v>104</v>
       </c>
       <c r="G15">
         <v>20</v>
@@ -2051,22 +2021,22 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>75</v>
+        <v>41</v>
       </c>
       <c r="B16" t="s">
-        <v>113</v>
+        <v>43</v>
       </c>
       <c r="C16" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="D16" t="s">
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="E16" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
       <c r="F16" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="G16">
         <v>10</v>
@@ -2077,22 +2047,22 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>75</v>
+        <v>41</v>
       </c>
       <c r="B17" t="s">
-        <v>113</v>
+        <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="D17" t="s">
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="E17" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
       <c r="F17" t="s">
-        <v>50</v>
+        <v>104</v>
       </c>
       <c r="G17">
         <v>20</v>
@@ -2103,22 +2073,22 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>114</v>
+        <v>47</v>
       </c>
       <c r="C18" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="D18" t="s">
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="E18" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
       <c r="F18" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="G18" s="14">
         <v>10</v>
@@ -2129,22 +2099,22 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="B19" t="s">
-        <v>114</v>
+        <v>47</v>
       </c>
       <c r="C19" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="D19" t="s">
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="E19" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
       <c r="F19" t="s">
-        <v>50</v>
+        <v>104</v>
       </c>
       <c r="G19">
         <v>20</v>
@@ -2155,22 +2125,22 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" t="s">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="B20" t="s">
-        <v>92</v>
+        <v>52</v>
       </c>
       <c r="C20" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D20" t="s">
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="E20" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
       <c r="F20" t="s">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="G20">
         <v>10</v>
@@ -2179,24 +2149,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="19">
+    <row r="21" spans="1:8" ht="19" customHeight="1">
       <c r="A21" t="s">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="B21" t="s">
-        <v>93</v>
+        <v>53</v>
       </c>
       <c r="C21" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D21" t="s">
-        <v>8</v>
+        <v>87</v>
       </c>
       <c r="E21" t="s">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>61</v>
+        <v>112</v>
       </c>
       <c r="G21">
         <v>5</v>
@@ -2207,22 +2177,22 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="B22" t="s">
-        <v>108</v>
+        <v>58</v>
       </c>
       <c r="C22" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D22" t="s">
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="E22" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
       <c r="F22" t="s">
-        <v>62</v>
+        <v>114</v>
       </c>
       <c r="G22">
         <v>10</v>
@@ -2234,20 +2204,20 @@
   </sheetData>
   <autoFilter ref="A1:H22" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
+  <conditionalFormatting sqref="C1:C11 C23:C1048576">
+    <cfRule type="duplicateValues" dxfId="4" priority="39"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C12:C13">
-    <cfRule type="duplicateValues" dxfId="4" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14:C19">
-    <cfRule type="duplicateValues" dxfId="3" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C20:C21">
-    <cfRule type="duplicateValues" dxfId="2" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C22">
-    <cfRule type="duplicateValues" dxfId="1" priority="41"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C23:C1048576 C1:C11">
-    <cfRule type="duplicateValues" dxfId="0" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="41"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/datasets/dict/dict.xlsx
+++ b/datasets/dict/dict.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yonghyunnam/coding/HanTalk_group/HanTalk/rule_example_auto/datasets/dict/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEAEEDA9-A34E-C046-B15C-9299EADC1DE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F620D5-45E9-8347-9B55-89E043398C62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="34560" windowHeight="21700" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/datasets/dict/dict.xlsx
+++ b/datasets/dict/dict.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yonghyunnam/coding/HanTalk_group/HanTalk/rule_example_auto/datasets/dict/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F620D5-45E9-8347-9B55-89E043398C62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{257478A6-957B-AF46-81A4-7B77E0846A24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="640" windowWidth="34560" windowHeight="21700" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="640" windowWidth="34560" windowHeight="21700" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="items" sheetId="1" r:id="rId1"/>
@@ -27,11 +27,218 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="126">
   <si>
     <t>e_id</t>
   </si>
   <si>
+    <t>ruleset_id</t>
+  </si>
+  <si>
+    <t>rule_id</t>
+  </si>
+  <si>
+    <t>stage</t>
+  </si>
+  <si>
+    <t>target</t>
+  </si>
+  <si>
+    <t>pattern</t>
+  </si>
+  <si>
+    <t>priority</t>
+  </si>
+  <si>
+    <t>hard_fail</t>
+  </si>
+  <si>
+    <t>component_id</t>
+  </si>
+  <si>
+    <t>ce002</t>
+  </si>
+  <si>
+    <t>rs_ce002_d01</t>
+  </si>
+  <si>
+    <t>r_ce002_d01</t>
+  </si>
+  <si>
+    <t>detect</t>
+  </si>
+  <si>
+    <t>raw_sentence</t>
+  </si>
+  <si>
+    <t>(?:[간갠갼걘건겐견곈곤관괜괸굔군권궨귄균근긘긴깐깬꺈꺤껀껜껸꼔꼰꽌꽨꾄꾠꾼꿘꿴뀐뀬끈끤낀난낸냔냰넌넨년녠논놘놴뇐뇬눈눤뉀뉜뉸는늰닌단댄댠댼던덴뎐뎬돈돤됀된됸둔둰뒌뒨듄든듼딘딴땐땬떈떤뗀뗜뗸똔똰뙌뙨뚄뚠뚼뛘뛴뜐뜬띈띤란랜랸럔런렌련롄론롼뢘뢴룐룬뤈뤤륀륜른린만맨먄먠먼멘면몐몬뫈뫤묀묜문뭔뭰뮌뮨믄믠민반밴뱐뱬번벤변볜본봔봰뵌뵨분붠붼뷘뷴븐븬빈빤뺀뺜뺸뻔뻰뼌뼨뽄뽠뽼뾘뾴뿐뿬쀈쀤쁀쁜쁸삔산샌샨섄선센션셴손솬쇈쇤숀순숸쉔쉰슌슨싄신싼쌘쌴썐썬쎈쎤쏀쏜쏸쐔쐰쑌쑨쒄쒠쒼쓘쓴씐씬안앤얀얜언엔연옌온완왠왼욘운원웬윈윤은읜인잔잰쟌쟨전젠젼졘존좐좬죈죤준줜줸쥔쥰즌즨진짠짼쨘쨴쩐쩬쪈쪤쫀쫜쫸쬔쬰쭌쭨쮄쮠쮼쯘쯴찐찬챈챤첀천첸쳔쳰촌촨쵄쵠쵼춘춴췐췬츈츤칀친칸캔캰컌컨켄켠켼콘콴쾐쾬쿈쿤퀀퀜퀸큔큰킌킨탄탠탼턘턴텐텬톈톤퇀퇜퇸툔툰퉌퉨튄튠튼틘틴판팬퍈퍤펀펜편폔폰퐌퐨푄푠푼풘풴퓐퓬픈픤핀한핸햔햰헌헨현혠혼환홴횐횬훈훤휀휜휸흔흰힌]|[ㄴ]|는)데(?:요)?(?![.?!~…]+)</t>
+  </si>
+  <si>
+    <t>r_ce002_d02</t>
+  </si>
+  <si>
+    <t>rs_ce002_v01</t>
+  </si>
+  <si>
+    <t>r_ce002_v03</t>
+  </si>
+  <si>
+    <t>verify</t>
+  </si>
+  <si>
+    <t>(?:는데다가|는\s*데다가|데다가)</t>
+  </si>
+  <si>
+    <t>r_ce002_v06</t>
+  </si>
+  <si>
+    <t>char_window</t>
+  </si>
+  <si>
+    <t>(?:가운데|그런데|군데|데다가|[펜엔]데믹)</t>
+  </si>
+  <si>
+    <t>r_ce002_v07</t>
+  </si>
+  <si>
+    <t>(?:^|[^가-힣])운데(?:$|[^가-힣])</t>
+  </si>
+  <si>
+    <t>ce003</t>
+  </si>
+  <si>
+    <t>rs_ce003_d01</t>
+  </si>
+  <si>
+    <t>r_ce003_d01</t>
+  </si>
+  <si>
+    <t>r_ce003_d02</t>
+  </si>
+  <si>
+    <t>rs_ce003_v01</t>
+  </si>
+  <si>
+    <t>r_ce003_v03</t>
+  </si>
+  <si>
+    <t>r_ce003_v06</t>
+  </si>
+  <si>
+    <t>r_ce003_v07</t>
+  </si>
+  <si>
+    <t>df004</t>
+  </si>
+  <si>
+    <t>rs_df004_d01</t>
+  </si>
+  <si>
+    <t>r_df004_d01</t>
+  </si>
+  <si>
+    <t>고(?!\s*정말)(?!\s*,)[^\n]{0,2}?(?&lt;!연)(?&lt;!월)(?&lt;!주)(?&lt;!아무)(?&lt;!회)(?&lt;!반)(?&lt;!막)(?&lt;!고추 )말(?!\s*(?:실수|다툼|싸움|보다|했|할|하|씀|해|한|함|을|은|이|에|도|만|들|끝|문|풍선|렸|릴|리|린|려|미|수|로|소|라|고|자|바))(?!(?:실수|다툼|싸움|보다|했|할|하|씀|해|한|함|을|은|이|에|도|만|들|끝|문|풍선|렸|릴|리|린|려|미|수|로|소|라|고|자|바))</t>
+  </si>
+  <si>
+    <t>df005</t>
+  </si>
+  <si>
+    <t>rs_df005_d01</t>
+  </si>
+  <si>
+    <t>r_df005_d01</t>
+  </si>
+  <si>
+    <t>pt001</t>
+  </si>
+  <si>
+    <t>rs_pt001_d01</t>
+  </si>
+  <si>
+    <t>r_pt001_d01</t>
+  </si>
+  <si>
+    <t>까지</t>
+  </si>
+  <si>
+    <t>r_pt001_d02</t>
+  </si>
+  <si>
+    <t>까\s*지</t>
+  </si>
+  <si>
+    <t>pt002</t>
+  </si>
+  <si>
+    <t>rs_pt002_d01</t>
+  </si>
+  <si>
+    <t>r_pt002_d01</t>
+  </si>
+  <si>
+    <t>r_pt002_d02</t>
+  </si>
+  <si>
+    <t>pt003</t>
+  </si>
+  <si>
+    <t>rs_pt003_d01</t>
+  </si>
+  <si>
+    <t>r_pt003_d01</t>
+  </si>
+  <si>
+    <t>r_pt003_d02</t>
+  </si>
+  <si>
+    <t>ce001</t>
+  </si>
+  <si>
+    <t>rs_ce001_d01</t>
+  </si>
+  <si>
+    <t>r_ce001_d01</t>
+  </si>
+  <si>
+    <t>(?:는다면|ㄴ다면|다면)</t>
+  </si>
+  <si>
+    <t>rs_ce001_v01</t>
+  </si>
+  <si>
+    <t>r_ce001_v01</t>
+  </si>
+  <si>
+    <t>(?:다면서|다\s*면서)</t>
+  </si>
+  <si>
+    <t>df003</t>
+  </si>
+  <si>
+    <t>rs_df003_d01</t>
+  </si>
+  <si>
+    <t>r_df003_d01</t>
+  </si>
+  <si>
+    <t>적(?:\s*(?:이|가|은|는|도|만|조차|까지))?[^\n]{0,200}?(?:있|없)</t>
+  </si>
+  <si>
+    <t>rs_df003_v01</t>
+  </si>
+  <si>
+    <t>r_df003_v01</t>
+  </si>
+  <si>
+    <t>component_right_context</t>
+  </si>
+  <si>
+    <t>^\s*(?:으로|인|일|에)</t>
+  </si>
+  <si>
+    <t>c2</t>
+  </si>
+  <si>
     <t>canonical_form</t>
   </si>
   <si>
@@ -62,9 +269,6 @@
     <t>gloss</t>
   </si>
   <si>
-    <t>ce002</t>
-  </si>
-  <si>
     <t>ㄴ/은/는데1</t>
   </si>
   <si>
@@ -80,33 +284,15 @@
     <t>c1</t>
   </si>
   <si>
-    <t>rs_ce002_d01</t>
-  </si>
-  <si>
-    <t>rs_ce002_v01</t>
-  </si>
-  <si>
     <t>앞절의 상황·배경을 제시하고 뒤절로 이어지게 하는 연결어미.</t>
   </si>
   <si>
-    <t>ce003</t>
-  </si>
-  <si>
     <t>ㄴ/은/는데2</t>
   </si>
   <si>
-    <t>rs_ce003_d01</t>
-  </si>
-  <si>
-    <t>rs_ce003_v01</t>
-  </si>
-  <si>
     <t>앞절과 뒤절이 대조·대립 혹은 양보적 전환, 반전되는 관계로 이어질 때 쓰는 연결어미.</t>
   </si>
   <si>
-    <t>df004</t>
-  </si>
-  <si>
     <t>고 말1</t>
   </si>
   <si>
@@ -119,105 +305,75 @@
     <t>c1;c2</t>
   </si>
   <si>
-    <t>rs_df004_d01</t>
-  </si>
-  <si>
     <t>일어나지 않았으면 좋았을 어떤 일이 끝내 일어났음을 나타내며 동시에 그 일이 일어난 것에 대한 화자의 안타까움을 나타낼 때 쓴다.</t>
   </si>
   <si>
-    <t>df005</t>
-  </si>
-  <si>
     <t>고 말2</t>
   </si>
   <si>
-    <t>rs_df005_d01</t>
-  </si>
-  <si>
     <t>이루기 쉽지 않은 어떤 일을 이루고자 하는 화자의 의지를 나타낼 때 쓴다.</t>
   </si>
   <si>
-    <t>pt001</t>
-  </si>
-  <si>
     <t>까지1</t>
   </si>
   <si>
     <t>ps_kkaji</t>
   </si>
   <si>
-    <t>rs_pt001_d01</t>
-  </si>
-  <si>
     <t>범위의 끝 지점이나 한계를 나타냄.</t>
   </si>
   <si>
-    <t>pt002</t>
-  </si>
-  <si>
     <t>까지2</t>
   </si>
   <si>
-    <t>rs_pt002_d01</t>
-  </si>
-  <si>
     <t>현재의 상태나 정도에서 더해지거나 더 나아감을 나타냄.</t>
   </si>
   <si>
-    <t>pt003</t>
-  </si>
-  <si>
     <t>까지3</t>
   </si>
   <si>
-    <t>rs_pt003_d01</t>
-  </si>
-  <si>
     <t>정상적인 정도를 지나침을 나타냄.</t>
   </si>
   <si>
-    <t>ce001</t>
-  </si>
-  <si>
     <t>다면</t>
   </si>
   <si>
     <t>b</t>
   </si>
   <si>
-    <t>rs_ce001_d01</t>
-  </si>
-  <si>
-    <t>rs_ce001_v01</t>
-  </si>
-  <si>
     <t>어떤 사실이나 상황을 가정하여 조건으로 삼는 것을 나타냄.</t>
   </si>
   <si>
-    <t>df003</t>
-  </si>
-  <si>
     <t>ㄴ/은 적 있/없</t>
   </si>
   <si>
     <t>c1;c2;c3</t>
   </si>
   <si>
-    <t>rs_df003_d01</t>
-  </si>
-  <si>
     <t>어떤 행위나 상태를 해 본 경험이 있거나 없음을 나타냄.</t>
   </si>
   <si>
     <t>comp_surf</t>
   </si>
   <si>
+    <t>comp_id</t>
+  </si>
+  <si>
+    <t>bridge_id</t>
+  </si>
+  <si>
     <t>is_required</t>
   </si>
   <si>
     <t>anchor_rank</t>
   </si>
   <si>
+    <t>comp_order</t>
+  </si>
+  <si>
+    <t>order_policy</t>
+  </si>
+  <si>
     <t>min_gap_to_next</t>
   </si>
   <si>
@@ -236,10 +392,10 @@
     <t>말</t>
   </si>
   <si>
-    <t>c2</t>
-  </si>
-  <si>
-    <t>까지</t>
+    <t>ㄴ/은</t>
+  </si>
+  <si>
+    <t>adnominal_n</t>
   </si>
   <si>
     <t>적</t>
@@ -249,165 +405,6 @@
   </si>
   <si>
     <t>c3</t>
-  </si>
-  <si>
-    <t>ruleset_id</t>
-  </si>
-  <si>
-    <t>rule_id</t>
-  </si>
-  <si>
-    <t>stage</t>
-  </si>
-  <si>
-    <t>target</t>
-  </si>
-  <si>
-    <t>pattern</t>
-  </si>
-  <si>
-    <t>priority</t>
-  </si>
-  <si>
-    <t>hard_fail</t>
-  </si>
-  <si>
-    <t>r_ce002_d01</t>
-  </si>
-  <si>
-    <t>detect</t>
-  </si>
-  <si>
-    <t>raw_sentence</t>
-  </si>
-  <si>
-    <t>(?:[간갠갼걘건겐견곈곤관괜괸굔군권궨귄균근긘긴깐깬꺈꺤껀껜껸꼔꼰꽌꽨꾄꾠꾼꿘꿴뀐뀬끈끤낀난낸냔냰넌넨년녠논놘놴뇐뇬눈눤뉀뉜뉸는늰닌단댄댠댼던덴뎐뎬돈돤됀된됸둔둰뒌뒨듄든듼딘딴땐땬떈떤뗀뗜뗸똔똰뙌뙨뚄뚠뚼뛘뛴뜐뜬띈띤란랜랸럔런렌련롄론롼뢘뢴룐룬뤈뤤륀륜른린만맨먄먠먼멘면몐몬뫈뫤묀묜문뭔뭰뮌뮨믄믠민반밴뱐뱬번벤변볜본봔봰뵌뵨분붠붼뷘뷴븐븬빈빤뺀뺜뺸뻔뻰뼌뼨뽄뽠뽼뾘뾴뿐뿬쀈쀤쁀쁜쁸삔산샌샨섄선센션셴손솬쇈쇤숀순숸쉔쉰슌슨싄신싼쌘쌴썐썬쎈쎤쏀쏜쏸쐔쐰쑌쑨쒄쒠쒼쓘쓴씐씬안앤얀얜언엔연옌온완왠왼욘운원웬윈윤은읜인잔잰쟌쟨전젠젼졘존좐좬죈죤준줜줸쥔쥰즌즨진짠짼쨘쨴쩐쩬쪈쪤쫀쫜쫸쬔쬰쭌쭨쮄쮠쮼쯘쯴찐찬챈챤첀천첸쳔쳰촌촨쵄쵠쵼춘춴췐췬츈츤칀친칸캔캰컌컨켄켠켼콘콴쾐쾬쿈쿤퀀퀜퀸큔큰킌킨탄탠탼턘턴텐텬톈톤퇀퇜퇸툔툰퉌퉨튄튠튼틘틴판팬퍈퍤펀펜편폔폰퐌퐨푄푠푼풘풴퓐퓬픈픤핀한핸햔햰헌헨현혠혼환홴횐횬훈훤휀휜휸흔흰힌]|[ㄴ]|는)데(?:요)?(?![.?!~…]+)</t>
-  </si>
-  <si>
-    <t>r_ce002_d02</t>
-  </si>
-  <si>
-    <t>r_ce002_v03</t>
-  </si>
-  <si>
-    <t>verify</t>
-  </si>
-  <si>
-    <t>(?:는데다가|는\s*데다가|데다가)</t>
-  </si>
-  <si>
-    <t>r_ce002_v06</t>
-  </si>
-  <si>
-    <t>char_window</t>
-  </si>
-  <si>
-    <t>(?:가운데|그런데|군데|데다가|[펜엔]데믹)</t>
-  </si>
-  <si>
-    <t>r_ce002_v07</t>
-  </si>
-  <si>
-    <t>(?:^|[^가-힣])운데(?:$|[^가-힣])</t>
-  </si>
-  <si>
-    <t>r_ce003_d01</t>
-  </si>
-  <si>
-    <t>r_ce003_d02</t>
-  </si>
-  <si>
-    <t>r_ce003_v03</t>
-  </si>
-  <si>
-    <t>r_ce003_v06</t>
-  </si>
-  <si>
-    <t>r_ce003_v07</t>
-  </si>
-  <si>
-    <t>r_df004_d01</t>
-  </si>
-  <si>
-    <t>고(?!\s*정말)(?!\s*,)[^\n]{0,2}?(?&lt;!연)(?&lt;!월)(?&lt;!주)(?&lt;!아무)(?&lt;!회)(?&lt;!반)(?&lt;!막)(?&lt;!고추 )말(?!\s*(?:실수|다툼|싸움|보다|했|할|하|씀|해|한|함|을|은|이|에|도|만|들|끝|문|풍선|렸|릴|리|린|려|미|수|로|소|라|고|자|바))(?!(?:실수|다툼|싸움|보다|했|할|하|씀|해|한|함|을|은|이|에|도|만|들|끝|문|풍선|렸|릴|리|린|려|미|수|로|소|라|고|자|바))</t>
-  </si>
-  <si>
-    <t>r_df005_d01</t>
-  </si>
-  <si>
-    <t>r_pt001_d01</t>
-  </si>
-  <si>
-    <t>r_pt001_d02</t>
-  </si>
-  <si>
-    <t>까\s*지</t>
-  </si>
-  <si>
-    <t>r_pt002_d01</t>
-  </si>
-  <si>
-    <t>r_pt002_d02</t>
-  </si>
-  <si>
-    <t>r_pt003_d01</t>
-  </si>
-  <si>
-    <t>r_pt003_d02</t>
-  </si>
-  <si>
-    <t>r_ce001_d01</t>
-  </si>
-  <si>
-    <t>(?:는다면|ㄴ다면|다면)</t>
-  </si>
-  <si>
-    <t>r_ce001_v01</t>
-  </si>
-  <si>
-    <t>(?:다면서|다\s*면서)</t>
-  </si>
-  <si>
-    <t>r_df003_d01</t>
-  </si>
-  <si>
-    <t>적(?:\s*(?:이|가|은|는|도|만|조차|까지))?[^\n]{0,200}?(?:있|없)</t>
-  </si>
-  <si>
-    <t>comp_order</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>order_policy</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>comp_id</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>bridge_id</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>adnominal_n</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄴ/은</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>df003</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄴ/은/는데</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>c1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -937,271 +934,274 @@
         <v>0</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>2</v>
+        <v>71</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>3</v>
+        <v>72</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>5</v>
+        <v>74</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>6</v>
+        <v>75</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>7</v>
+        <v>76</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>9</v>
+        <v>78</v>
       </c>
       <c r="K1" s="11" t="s">
-        <v>10</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="12" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>13</v>
+        <v>81</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>15</v>
+        <v>83</v>
       </c>
       <c r="H2" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="12" t="s">
-        <v>18</v>
-      </c>
       <c r="K2" s="12" t="s">
-        <v>19</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="12" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>13</v>
+        <v>81</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>15</v>
+        <v>83</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="12" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>26</v>
+        <v>88</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>13</v>
+        <v>81</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>29</v>
+        <v>91</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>31</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="12" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>33</v>
+        <v>93</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>13</v>
+        <v>81</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>29</v>
+        <v>91</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="19" customHeight="1">
       <c r="A6" s="12" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>37</v>
+        <v>95</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>13</v>
+        <v>81</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>15</v>
+        <v>83</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K6" s="13" t="s">
-        <v>40</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="19" customHeight="1">
       <c r="A7" s="12" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>13</v>
+        <v>81</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>15</v>
+        <v>83</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="K7" s="13" t="s">
-        <v>44</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="19" customHeight="1">
       <c r="A8" s="12" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>13</v>
+        <v>81</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>15</v>
+        <v>83</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="12" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>50</v>
+        <v>102</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>15</v>
+        <v>83</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="K9" s="12" t="s">
-        <v>54</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="12" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>56</v>
+        <v>105</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>58</v>
+        <v>62</v>
+      </c>
+      <c r="J10" s="12" t="s">
+        <v>65</v>
       </c>
       <c r="K10" s="12" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -1231,46 +1231,46 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>61</v>
+        <v>111</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>62</v>
+        <v>112</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C2" t="s">
-        <v>123</v>
+        <v>84</v>
       </c>
       <c r="D2"/>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -1279,22 +1279,22 @@
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="D3"/>
       <c r="E3" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -1303,22 +1303,22 @@
         <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>119</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="D4"/>
       <c r="E4" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="F4">
         <v>2</v>
@@ -1327,7 +1327,7 @@
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1338,17 +1338,17 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>120</v>
       </c>
       <c r="C5" t="s">
         <v>69</v>
       </c>
       <c r="D5"/>
       <c r="E5" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -1357,24 +1357,24 @@
         <v>2</v>
       </c>
       <c r="H5" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="I5"/>
       <c r="J5"/>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>119</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="D6"/>
       <c r="E6" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="F6">
         <v>2</v>
@@ -1383,7 +1383,7 @@
         <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1394,17 +1394,17 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>120</v>
       </c>
       <c r="C7" t="s">
         <v>69</v>
       </c>
       <c r="D7"/>
       <c r="E7" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -1413,24 +1413,24 @@
         <v>2</v>
       </c>
       <c r="H7" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="D8"/>
       <c r="E8" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -1439,22 +1439,22 @@
         <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="D9"/>
       <c r="E9" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -1463,22 +1463,22 @@
         <v>1</v>
       </c>
       <c r="H9" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="D10"/>
       <c r="E10" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -1487,22 +1487,22 @@
         <v>1</v>
       </c>
       <c r="H10" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B11" t="s">
-        <v>50</v>
+        <v>102</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="D11"/>
       <c r="E11" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -1511,24 +1511,24 @@
         <v>1</v>
       </c>
       <c r="H11" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" t="s">
         <v>121</v>
       </c>
-      <c r="B12" t="s">
-        <v>120</v>
-      </c>
       <c r="C12" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="D12" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E12" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1537,28 +1537,28 @@
         <v>1</v>
       </c>
       <c r="H12" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>123</v>
       </c>
       <c r="C13" t="s">
         <v>69</v>
       </c>
       <c r="D13"/>
       <c r="E13" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="F13">
         <v>2</v>
@@ -1567,28 +1567,28 @@
         <v>2</v>
       </c>
       <c r="H13" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
       <c r="J13">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>124</v>
       </c>
       <c r="C14" t="s">
-        <v>73</v>
+        <v>125</v>
       </c>
       <c r="D14"/>
       <c r="E14" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -1597,7 +1597,7 @@
         <v>3</v>
       </c>
       <c r="H14" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -1610,16 +1610,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="8" customWidth="1"/>
     <col min="2" max="2" width="14.5703125" style="8" customWidth="1"/>
     <col min="3" max="3" width="15.85546875" style="8" customWidth="1"/>
-    <col min="5" max="5" width="13.85546875" style="8" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" style="8" customWidth="1"/>
     <col min="6" max="6" width="105.5703125" style="5" customWidth="1"/>
     <col min="7" max="7" width="7.42578125" style="8" customWidth="1"/>
     <col min="8" max="8" width="9" style="2" customWidth="1"/>
+    <col min="9" max="9" width="13.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="19" customHeight="1">
@@ -1627,45 +1628,48 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>74</v>
+        <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>75</v>
+        <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>76</v>
+        <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>77</v>
+        <v>4</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>78</v>
+        <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>79</v>
+        <v>6</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>80</v>
+        <v>7</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" t="s">
-        <v>81</v>
-      </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>84</v>
+        <v>14</v>
       </c>
       <c r="G2">
         <v>10</v>
@@ -1677,22 +1681,22 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>84</v>
+        <v>14</v>
       </c>
       <c r="G3">
         <v>20</v>
@@ -1704,22 +1708,22 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
         <v>18</v>
       </c>
-      <c r="C4" t="s">
-        <v>86</v>
-      </c>
-      <c r="D4" t="s">
-        <v>87</v>
-      </c>
       <c r="E4" t="s">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="F4" t="s">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="G4">
         <v>50</v>
@@ -1731,22 +1735,22 @@
     </row>
     <row r="5" spans="1:9" ht="19" customHeight="1">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
         <v>18</v>
       </c>
-      <c r="C5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D5" t="s">
-        <v>87</v>
-      </c>
       <c r="E5" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -1758,22 +1762,22 @@
     </row>
     <row r="6" spans="1:9" ht="19" customHeight="1">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="s">
         <v>18</v>
       </c>
-      <c r="C6" t="s">
-        <v>92</v>
-      </c>
-      <c r="D6" t="s">
-        <v>87</v>
-      </c>
       <c r="E6" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>93</v>
+        <v>24</v>
       </c>
       <c r="G6">
         <v>6</v>
@@ -1785,22 +1789,22 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>82</v>
+        <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="F7" t="s">
-        <v>84</v>
+        <v>14</v>
       </c>
       <c r="G7">
         <v>10</v>
@@ -1812,22 +1816,22 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>82</v>
+        <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="F8" t="s">
-        <v>84</v>
+        <v>14</v>
       </c>
       <c r="G8">
         <v>20</v>
@@ -1839,22 +1843,22 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>18</v>
       </c>
       <c r="E9" t="s">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="F9" t="s">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="G9">
         <v>50</v>
@@ -1865,22 +1869,22 @@
     </row>
     <row r="10" spans="1:9" ht="19" customHeight="1">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>97</v>
+        <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>87</v>
+        <v>18</v>
       </c>
       <c r="E10" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -1891,22 +1895,22 @@
     </row>
     <row r="11" spans="1:9" ht="19" customHeight="1">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>98</v>
+        <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>87</v>
+        <v>18</v>
       </c>
       <c r="E11" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>93</v>
+        <v>24</v>
       </c>
       <c r="G11">
         <v>6</v>
@@ -1917,22 +1921,22 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>99</v>
+        <v>35</v>
       </c>
       <c r="D12" t="s">
-        <v>82</v>
+        <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="F12" t="s">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="G12">
         <v>10</v>
@@ -1943,22 +1947,22 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C13" t="s">
-        <v>101</v>
+        <v>39</v>
       </c>
       <c r="D13" t="s">
-        <v>82</v>
+        <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="F13" t="s">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="G13">
         <v>10</v>
@@ -1969,22 +1973,22 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C14" t="s">
-        <v>102</v>
+        <v>42</v>
       </c>
       <c r="D14" t="s">
-        <v>82</v>
+        <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="F14" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="G14">
         <v>10</v>
@@ -1995,22 +1999,22 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>44</v>
       </c>
       <c r="D15" t="s">
-        <v>82</v>
+        <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="F15" t="s">
-        <v>104</v>
+        <v>45</v>
       </c>
       <c r="G15">
         <v>20</v>
@@ -2021,22 +2025,22 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B16" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" t="s">
         <v>43</v>
-      </c>
-      <c r="C16" t="s">
-        <v>105</v>
-      </c>
-      <c r="D16" t="s">
-        <v>82</v>
-      </c>
-      <c r="E16" t="s">
-        <v>83</v>
-      </c>
-      <c r="F16" t="s">
-        <v>70</v>
       </c>
       <c r="G16">
         <v>10</v>
@@ -2045,24 +2049,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B17" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C17" t="s">
-        <v>106</v>
+        <v>49</v>
       </c>
       <c r="D17" t="s">
-        <v>82</v>
+        <v>12</v>
       </c>
       <c r="E17" t="s">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="F17" t="s">
-        <v>104</v>
+        <v>45</v>
       </c>
       <c r="G17">
         <v>20</v>
@@ -2071,24 +2075,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C18" t="s">
-        <v>107</v>
+        <v>52</v>
       </c>
       <c r="D18" t="s">
-        <v>82</v>
+        <v>12</v>
       </c>
       <c r="E18" t="s">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="F18" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="G18" s="14">
         <v>10</v>
@@ -2097,24 +2101,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:9">
       <c r="A19" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" t="s">
         <v>45</v>
-      </c>
-      <c r="B19" t="s">
-        <v>47</v>
-      </c>
-      <c r="C19" t="s">
-        <v>108</v>
-      </c>
-      <c r="D19" t="s">
-        <v>82</v>
-      </c>
-      <c r="E19" t="s">
-        <v>83</v>
-      </c>
-      <c r="F19" t="s">
-        <v>104</v>
       </c>
       <c r="G19">
         <v>20</v>
@@ -2123,24 +2127,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B20" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C20" t="s">
-        <v>109</v>
+        <v>56</v>
       </c>
       <c r="D20" t="s">
-        <v>82</v>
+        <v>12</v>
       </c>
       <c r="E20" t="s">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="F20" t="s">
-        <v>110</v>
+        <v>57</v>
       </c>
       <c r="G20">
         <v>10</v>
@@ -2149,24 +2153,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="19" customHeight="1">
+    <row r="21" spans="1:9" ht="19" customHeight="1">
       <c r="A21" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B21" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C21" t="s">
-        <v>111</v>
+        <v>59</v>
       </c>
       <c r="D21" t="s">
-        <v>87</v>
+        <v>18</v>
       </c>
       <c r="E21" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="G21">
         <v>5</v>
@@ -2175,36 +2179,65 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B22" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C22" t="s">
-        <v>113</v>
+        <v>63</v>
       </c>
       <c r="D22" t="s">
-        <v>82</v>
+        <v>12</v>
       </c>
       <c r="E22" t="s">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="F22" t="s">
-        <v>114</v>
+        <v>64</v>
       </c>
       <c r="G22">
         <v>10</v>
       </c>
       <c r="H22" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="19" customHeight="1">
+      <c r="A23" t="s">
+        <v>61</v>
+      </c>
+      <c r="B23" t="s">
+        <v>65</v>
+      </c>
+      <c r="C23" t="s">
+        <v>66</v>
+      </c>
+      <c r="D23" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="G23">
+        <v>5</v>
+      </c>
+      <c r="H23" t="b">
+        <v>1</v>
+      </c>
+      <c r="I23" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H22" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="C1:C11 C23:C1048576">
+  <conditionalFormatting sqref="C1:C11 C23:C1048576 D23:E23">
     <cfRule type="duplicateValues" dxfId="4" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C12:C13">
